--- a/ner/sheets/people.xlsx
+++ b/ner/sheets/people.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11008"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ia\HuC$\home\NinaL\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/me/github/HuygensING/suriano/ner/sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B3146BB-8BC6-F349-9067-FE2565D236F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="10650"/>
+    <workbookView xWindow="20" yWindow="520" windowWidth="33560" windowHeight="18600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="1033">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="1036">
   <si>
     <t>PRIMARY NAME</t>
   </si>
@@ -3711,11 +3712,20 @@
   <si>
     <t>Domizio Caracciolo, Marchese della Bella</t>
   </si>
+  <si>
+    <t>KIND</t>
+  </si>
+  <si>
+    <t>One of the values PER, LOC, ORG, MISC</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3922,9 +3932,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3978,7 +3988,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3986,25 +3996,21 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4016,14 +4022,11 @@
     <xf numFmtId="49" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Heading 1 1" xfId="1"/>
+    <cellStyle name="Heading 1 1" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4300,1487 +4303,1689 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P286"/>
-  <sheetFormatPr defaultColWidth="5.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q286"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="5.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.90625" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" customWidth="1"/>
-    <col min="3" max="3" width="26.7265625" customWidth="1"/>
-    <col min="12" max="12" width="27.36328125" style="41" customWidth="1"/>
-    <col min="13" max="13" width="17.08984375" style="41" customWidth="1"/>
-    <col min="14" max="14" width="15.54296875" customWidth="1"/>
-    <col min="15" max="15" width="10.36328125" style="41" customWidth="1"/>
+    <col min="1" max="2" width="33.83203125" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+    <col min="13" max="13" width="27.33203125" style="29" customWidth="1"/>
+    <col min="14" max="14" width="17.1640625" style="29" customWidth="1"/>
+    <col min="15" max="15" width="15.5" customWidth="1"/>
+    <col min="16" max="16" width="10.33203125" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="9" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:16" s="9" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="18" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" s="18" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="10" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="11" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="E2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="F2" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="G2" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="H2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="I2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="J2" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="K2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="L2" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="M2" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="N2" s="16" t="s">
         <v>1030</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="O2" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="P2" s="17" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:15" s="21" customFormat="1" ht="364.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" s="21" customFormat="1" ht="384" x14ac:dyDescent="0.2">
       <c r="A3" s="19" t="s">
         <v>27</v>
       </c>
       <c r="B3" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="D3" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="19">
+      <c r="E3" s="19">
         <v>1580</v>
       </c>
-      <c r="F3" s="19"/>
       <c r="G3" s="19"/>
       <c r="H3" s="19"/>
-      <c r="J3" s="19"/>
+      <c r="I3" s="19"/>
       <c r="K3" s="19"/>
-      <c r="L3" s="22" t="s">
+      <c r="L3" s="19"/>
+      <c r="M3" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="30"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="22" t="s">
+      <c r="N3" s="29"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="22" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="19" t="s">
         <v>32</v>
       </c>
       <c r="B4" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="D4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="H4" s="19"/>
-    </row>
-    <row r="5" spans="1:15" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E4" s="19"/>
+      <c r="I4" s="19"/>
+    </row>
+    <row r="5" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C5" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="D5" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="L5" s="22" t="s">
+      <c r="E5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="M5" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="M5" s="22"/>
-      <c r="N5" s="20" t="s">
+      <c r="N5" s="22"/>
+      <c r="O5" s="20" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="20" t="s">
+      <c r="B6" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C6" s="19"/>
+      <c r="D6" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="20" t="s">
+      <c r="E6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="20" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
         <v>43</v>
       </c>
       <c r="B7" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="D7" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19" t="s">
+      <c r="E7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="19"/>
       <c r="I7" s="19"/>
       <c r="J7" s="19"/>
       <c r="K7" s="19"/>
-      <c r="L7" s="22"/>
-    </row>
-    <row r="8" spans="1:15" ht="39.5" x14ac:dyDescent="0.35">
+      <c r="L7" s="19"/>
+      <c r="M7" s="22"/>
+    </row>
+    <row r="8" spans="1:16" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="B8" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D8" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="19">
+      <c r="E8" s="19">
         <v>1574</v>
       </c>
-      <c r="F8" s="19"/>
       <c r="G8" s="19"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="J8" s="19"/>
       <c r="K8" s="19"/>
-      <c r="L8" s="22"/>
-    </row>
-    <row r="9" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L8" s="19"/>
+      <c r="M8" s="22"/>
+    </row>
+    <row r="9" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="B9" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D9" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="19">
+      <c r="E9" s="19">
         <v>1592</v>
       </c>
-      <c r="F9" s="19"/>
       <c r="G9" s="19"/>
       <c r="H9" s="19"/>
       <c r="I9" s="19"/>
       <c r="J9" s="19"/>
       <c r="K9" s="19"/>
-      <c r="L9" s="22" t="s">
+      <c r="L9" s="19"/>
+      <c r="M9" s="22" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>52</v>
       </c>
       <c r="B10" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C10" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="D10" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="19">
+      <c r="E10" s="19">
         <v>1500</v>
       </c>
-      <c r="H10" s="19"/>
-    </row>
-    <row r="11" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="I10" s="19"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="20" t="s">
         <v>55</v>
       </c>
       <c r="B11" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="D11" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="19">
+      <c r="E11" s="19">
         <v>1528</v>
       </c>
-      <c r="E11" s="19"/>
       <c r="F11" s="19"/>
       <c r="G11" s="19"/>
       <c r="H11" s="19"/>
       <c r="I11" s="19"/>
       <c r="J11" s="19"/>
       <c r="K11" s="19"/>
-      <c r="L11" s="22"/>
-    </row>
-    <row r="12" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="L11" s="19"/>
+      <c r="M11" s="22"/>
+    </row>
+    <row r="12" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" s="20" t="s">
         <v>58</v>
       </c>
       <c r="B12" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C12" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="D12" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="19">
+      <c r="E12" s="19">
         <v>1553</v>
       </c>
-      <c r="H12" s="19"/>
-      <c r="L12" s="22"/>
-    </row>
-    <row r="13" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="I12" s="19"/>
+      <c r="M12" s="22"/>
+    </row>
+    <row r="13" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A13" s="20" t="s">
         <v>61</v>
       </c>
       <c r="B13" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C13" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="D13" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="19">
+      <c r="E13" s="19">
         <v>1550</v>
       </c>
-      <c r="E13" s="19"/>
       <c r="F13" s="19"/>
       <c r="G13" s="19"/>
       <c r="H13" s="19"/>
       <c r="I13" s="19"/>
       <c r="J13" s="19"/>
       <c r="K13" s="19"/>
-      <c r="L13" s="22" t="s">
+      <c r="L13" s="19"/>
+      <c r="M13" s="22" t="s">
         <v>1031</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="20" t="s">
         <v>64</v>
       </c>
       <c r="B14" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="D14" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="19">
+      <c r="E14" s="19">
         <v>1577</v>
       </c>
-      <c r="E14" s="19"/>
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
       <c r="H14" s="19"/>
       <c r="I14" s="19"/>
       <c r="J14" s="19"/>
       <c r="K14" s="19"/>
-      <c r="L14" s="22"/>
-    </row>
-    <row r="15" spans="1:15" ht="68.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L14" s="19"/>
+      <c r="M14" s="22"/>
+    </row>
+    <row r="15" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="23" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="D15" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="D15" s="19">
+      <c r="E15" s="19">
         <v>1580</v>
       </c>
-      <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
       <c r="H15" s="19"/>
-      <c r="M15" s="22" t="s">
+      <c r="I15" s="19"/>
+      <c r="N15" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="N15" s="19" t="s">
+      <c r="O15" s="19" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="20" t="s">
+      <c r="B16" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="19">
+      <c r="E16" s="19">
         <v>1558</v>
       </c>
-      <c r="E16" s="19"/>
       <c r="F16" s="19"/>
       <c r="G16" s="19"/>
       <c r="H16" s="19"/>
-    </row>
-    <row r="17" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I16" s="19"/>
+    </row>
+    <row r="17" spans="1:17" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="24" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C17" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="D17" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="19">
+      <c r="E17" s="19">
         <v>1588</v>
       </c>
-      <c r="E17" s="19"/>
       <c r="F17" s="19"/>
       <c r="G17" s="19"/>
-      <c r="H17" s="19">
+      <c r="H17" s="19"/>
+      <c r="I17" s="19">
         <v>1622</v>
       </c>
-      <c r="L17" s="22" t="s">
+      <c r="M17" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="N17" s="20" t="s">
+      <c r="O17" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="O17" s="22"/>
-    </row>
-    <row r="18" spans="1:16" ht="39.5" x14ac:dyDescent="0.35">
+      <c r="P17" s="22"/>
+    </row>
+    <row r="18" spans="1:17" ht="45" x14ac:dyDescent="0.2">
       <c r="A18" s="19" t="s">
         <v>79</v>
       </c>
       <c r="B18" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C18" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="D18" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="D18" s="19">
+      <c r="E18" s="19">
         <v>1551</v>
       </c>
-      <c r="E18" s="19"/>
       <c r="F18" s="19"/>
       <c r="G18" s="19"/>
       <c r="H18" s="19"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="I18" s="19"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="19" t="s">
         <v>82</v>
       </c>
       <c r="B19" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C19" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="D19" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="19">
+      <c r="E19" s="19">
         <v>1571</v>
       </c>
-      <c r="E19" s="19"/>
       <c r="F19" s="19"/>
       <c r="G19" s="19"/>
       <c r="H19" s="19"/>
       <c r="I19" s="19"/>
       <c r="J19" s="19"/>
-    </row>
-    <row r="20" spans="1:16" ht="78.5" x14ac:dyDescent="0.35">
+      <c r="K19" s="19"/>
+    </row>
+    <row r="20" spans="1:17" ht="75" x14ac:dyDescent="0.2">
       <c r="A20" s="19" t="s">
         <v>85</v>
       </c>
       <c r="B20" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C20" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="D20" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="19">
+      <c r="E20" s="19">
         <v>1554</v>
       </c>
-      <c r="E20" s="19"/>
       <c r="F20" s="19"/>
       <c r="G20" s="19"/>
       <c r="H20" s="19"/>
       <c r="I20" s="19"/>
       <c r="J20" s="19"/>
       <c r="K20" s="19"/>
-      <c r="L20" s="22" t="s">
+      <c r="L20" s="19"/>
+      <c r="M20" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="M20" s="22"/>
-      <c r="N20" s="20" t="s">
+      <c r="N20" s="22"/>
+      <c r="O20" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="O20" s="22"/>
-      <c r="P20" s="19"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="P20" s="22"/>
+      <c r="Q20" s="19"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="19" t="s">
         <v>90</v>
       </c>
       <c r="B21" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C21" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="D21" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="D21" s="19">
+      <c r="E21" s="19">
         <v>1563</v>
       </c>
-      <c r="E21" s="19"/>
       <c r="F21" s="19"/>
       <c r="G21" s="19"/>
       <c r="H21" s="19"/>
       <c r="I21" s="19"/>
       <c r="J21" s="19"/>
       <c r="K21" s="19"/>
-      <c r="L21" s="22"/>
-    </row>
-    <row r="22" spans="1:16" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="L21" s="19"/>
+      <c r="M21" s="22"/>
+    </row>
+    <row r="22" spans="1:17" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="20" t="s">
+      <c r="B22" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C22" s="19"/>
+      <c r="D22" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="19">
+      <c r="E22" s="19">
         <v>1590</v>
       </c>
-      <c r="E22" s="19"/>
       <c r="F22" s="19"/>
       <c r="G22" s="19"/>
       <c r="H22" s="19"/>
       <c r="I22" s="19"/>
-      <c r="L22" s="22" t="s">
+      <c r="J22" s="19"/>
+      <c r="M22" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="N22" s="19" t="s">
+      <c r="O22" s="19" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="B23" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D23" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="H23" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="N23" s="19" t="s">
+      <c r="O23" s="19" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C24" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="D24" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="D24" s="19">
+      <c r="E24" s="19">
         <v>1588</v>
       </c>
-      <c r="H24" s="19"/>
-      <c r="M24" s="22" t="s">
+      <c r="I24" s="19"/>
+      <c r="N24" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="N24" s="20" t="s">
+      <c r="O24" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="O24" s="30" t="s">
+      <c r="P24" s="29" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="91.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" ht="90" x14ac:dyDescent="0.2">
       <c r="A25" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="B25" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D25" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="D25" s="19">
+      <c r="E25" s="19">
         <v>1561</v>
       </c>
-      <c r="E25" s="19"/>
       <c r="F25" s="19"/>
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
-      <c r="N25" s="20" t="s">
+      <c r="I25" s="19"/>
+      <c r="O25" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="O25" s="22" t="s">
+      <c r="P25" s="22" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="91.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" ht="90" x14ac:dyDescent="0.2">
       <c r="A26" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="26" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C26" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="D26" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="D26" s="19">
+      <c r="E26" s="19">
         <v>1573</v>
       </c>
-      <c r="E26" s="19"/>
       <c r="F26" s="19"/>
       <c r="G26" s="19"/>
       <c r="H26" s="19"/>
-      <c r="M26" s="22" t="s">
+      <c r="I26" s="19"/>
+      <c r="N26" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="N26" s="19" t="s">
+      <c r="O26" s="19" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="91.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" ht="105" x14ac:dyDescent="0.2">
       <c r="A27" s="19" t="s">
         <v>116</v>
       </c>
       <c r="B27" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C27" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="D27" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D27" s="19">
+      <c r="E27" s="19">
         <v>1575</v>
       </c>
-      <c r="E27" s="19"/>
       <c r="F27" s="19"/>
       <c r="G27" s="19"/>
       <c r="H27" s="19"/>
-      <c r="L27" s="22" t="s">
+      <c r="I27" s="19"/>
+      <c r="M27" s="22" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" ht="45" x14ac:dyDescent="0.2">
       <c r="A28" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="B28" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D28" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="D28" s="19">
+      <c r="E28" s="19">
         <v>1601</v>
       </c>
-      <c r="E28" s="19"/>
       <c r="F28" s="19"/>
       <c r="G28" s="19"/>
       <c r="H28" s="19"/>
-      <c r="L28" s="22" t="s">
+      <c r="I28" s="19"/>
+      <c r="M28" s="22" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" ht="45" x14ac:dyDescent="0.2">
       <c r="A29" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="20" t="s">
+      <c r="B29" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="D29" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="D29" s="19">
+      <c r="E29" s="19">
         <v>1606</v>
       </c>
-      <c r="E29" s="19"/>
       <c r="F29" s="19"/>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
-      <c r="L29" s="22" t="s">
+      <c r="J29" s="19"/>
+      <c r="M29" s="22" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="19" t="s">
         <v>126</v>
       </c>
       <c r="B30" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="D30" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="D30" s="19">
+      <c r="E30" s="19">
         <v>1587</v>
       </c>
-      <c r="H30" s="19"/>
-      <c r="L30" s="22" t="s">
+      <c r="I30" s="19"/>
+      <c r="M30" s="22" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="65.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" ht="75" x14ac:dyDescent="0.2">
       <c r="A31" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="B31" s="28"/>
-      <c r="D31" s="19">
+      <c r="B31" s="27" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E31" s="19">
         <v>1598</v>
       </c>
-      <c r="E31" s="19"/>
       <c r="F31" s="19"/>
       <c r="G31" s="19"/>
       <c r="H31" s="19"/>
-      <c r="L31" s="22" t="s">
+      <c r="I31" s="19"/>
+      <c r="M31" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="M31" s="22" t="s">
+      <c r="N31" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="N31" s="20" t="s">
+      <c r="O31" s="20" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="90.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" ht="90.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="19" t="s">
         <v>134</v>
       </c>
       <c r="B32" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C32" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="D32" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="D32" s="19"/>
       <c r="E32" s="19"/>
       <c r="F32" s="19"/>
-      <c r="G32" s="19" t="s">
+      <c r="G32" s="19"/>
+      <c r="H32" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="H32" s="19"/>
       <c r="I32" s="19"/>
       <c r="J32" s="19"/>
       <c r="K32" s="19"/>
-      <c r="L32" s="22" t="s">
+      <c r="L32" s="19"/>
+      <c r="M32" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="N32" s="19" t="s">
+      <c r="O32" s="19" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="65.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16" ht="75" x14ac:dyDescent="0.2">
       <c r="A33" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="20" t="s">
+      <c r="B33" s="27" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C33" s="19"/>
+      <c r="D33" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="M33" s="22" t="s">
+      <c r="N33" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="N33" s="20" t="s">
+      <c r="O33" s="20" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="78.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" ht="75" x14ac:dyDescent="0.2">
       <c r="A34" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="B34" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D34" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="D34" s="19">
+      <c r="E34" s="19">
         <v>1545</v>
       </c>
-      <c r="E34" s="19"/>
       <c r="F34" s="19"/>
       <c r="G34" s="19"/>
       <c r="H34" s="19"/>
-      <c r="L34" s="22" t="s">
+      <c r="I34" s="19"/>
+      <c r="M34" s="22" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A35" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C35" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="C35" s="20" t="s">
+      <c r="D35" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="D35" s="19">
+      <c r="E35" s="19">
         <v>1553</v>
       </c>
-      <c r="H35" s="19"/>
-    </row>
-    <row r="36" spans="1:15" ht="87.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I35" s="19"/>
+    </row>
+    <row r="36" spans="1:16" ht="87.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="C36" s="20" t="s">
+      <c r="B36" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D36" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="D36" s="19">
+      <c r="E36" s="19">
         <v>1567</v>
       </c>
-      <c r="E36" s="19"/>
       <c r="F36" s="19"/>
       <c r="G36" s="19"/>
       <c r="H36" s="19"/>
-      <c r="L36" s="22" t="s">
+      <c r="I36" s="19"/>
+      <c r="M36" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="M36" s="22" t="s">
+      <c r="N36" s="22" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A37" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="C37" s="20" t="s">
+      <c r="B37" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D37" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="D37" s="19">
+      <c r="E37" s="19">
         <v>1569</v>
       </c>
-      <c r="E37" s="19"/>
       <c r="F37" s="19"/>
       <c r="G37" s="19"/>
       <c r="H37" s="19"/>
-    </row>
-    <row r="38" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+      <c r="I37" s="19"/>
+    </row>
+    <row r="38" spans="1:16" ht="60" x14ac:dyDescent="0.2">
       <c r="A38" s="20" t="s">
         <v>156</v>
       </c>
       <c r="B38" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C38" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="C38" s="20" t="s">
+      <c r="D38" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="D38" s="19">
+      <c r="E38" s="19">
         <v>1560</v>
       </c>
-      <c r="E38" s="19"/>
       <c r="F38" s="19"/>
       <c r="G38" s="19"/>
       <c r="H38" s="19"/>
-      <c r="N38" s="20" t="s">
+      <c r="I38" s="19"/>
+      <c r="O38" s="20" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:16" ht="45" x14ac:dyDescent="0.2">
       <c r="A39" s="20" t="s">
         <v>160</v>
       </c>
       <c r="B39" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C39" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="D39" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="D39" s="19">
+      <c r="E39" s="19">
         <v>1588</v>
       </c>
-      <c r="E39" s="19"/>
       <c r="F39" s="19"/>
       <c r="G39" s="19"/>
       <c r="H39" s="19"/>
-      <c r="M39" s="22" t="s">
+      <c r="I39" s="19"/>
+      <c r="N39" s="22" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16" ht="96" x14ac:dyDescent="0.2">
       <c r="A40" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="B40" s="20" t="s">
+      <c r="B40" s="27" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C40" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="C40" s="20" t="s">
+      <c r="D40" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="D40" s="19">
+      <c r="E40" s="19">
         <v>1560</v>
       </c>
-      <c r="E40" s="19"/>
       <c r="F40" s="19"/>
       <c r="G40" s="19"/>
       <c r="H40" s="19"/>
-      <c r="M40" s="22" t="s">
+      <c r="I40" s="19"/>
+      <c r="N40" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="O40" s="41" t="s">
+      <c r="P40" s="29" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="134.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16" ht="134.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="19" t="s">
         <v>169</v>
       </c>
       <c r="B41" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C41" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="C41" s="26" t="s">
+      <c r="D41" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="J41" s="19" t="s">
+      <c r="K41" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="L41" s="22" t="s">
+      <c r="M41" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="M41" s="22" t="s">
+      <c r="N41" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="N41" s="20" t="s">
+      <c r="O41" s="20" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="95.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:16" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="26" t="s">
+      <c r="B42" s="27" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C42" s="19"/>
+      <c r="D42" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="J42" s="19"/>
-      <c r="L42" s="22" t="s">
+      <c r="K42" s="19"/>
+      <c r="M42" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="M42" s="22" t="s">
+      <c r="N42" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="N42" s="20" t="s">
+      <c r="O42" s="20" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="81.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" ht="81.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="B43" s="19" t="s">
+      <c r="B43" s="27" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C43" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="C43" s="26" t="s">
+      <c r="D43" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="G43" s="19" t="s">
+      <c r="H43" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="J43" s="19"/>
-      <c r="L43" s="22" t="s">
+      <c r="K43" s="19"/>
+      <c r="M43" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="M43" s="22" t="s">
+      <c r="N43" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="N43" s="20" t="s">
+      <c r="O43" s="20" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="91.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:16" ht="90" x14ac:dyDescent="0.2">
       <c r="A44" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="B44" s="19" t="s">
+      <c r="B44" s="27" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C44" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="D44" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="J44" s="19"/>
-      <c r="L44" s="22"/>
-      <c r="M44" s="22" t="s">
+      <c r="K44" s="19"/>
+      <c r="M44" s="22"/>
+      <c r="N44" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="N44" s="20" t="s">
+      <c r="O44" s="20" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="117.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:16" ht="135" x14ac:dyDescent="0.2">
       <c r="A45" s="19" t="s">
         <v>190</v>
       </c>
       <c r="B45" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C45" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="C45" s="26" t="s">
+      <c r="D45" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>193</v>
       </c>
-      <c r="M45" s="22" t="s">
+      <c r="N45" s="22" t="s">
         <v>194</v>
       </c>
-      <c r="N45" s="20" t="s">
+      <c r="O45" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="O45" s="41" t="s">
+      <c r="P45" s="29" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="56.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:16" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="20" t="s">
         <v>197</v>
       </c>
       <c r="B46" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C46" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="D46" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="D46" s="19">
+      <c r="E46" s="19">
         <v>1553</v>
       </c>
-      <c r="E46" s="19"/>
       <c r="F46" s="19"/>
       <c r="G46" s="19"/>
-      <c r="H46" s="19">
+      <c r="H46" s="19"/>
+      <c r="I46" s="19">
         <v>1630</v>
       </c>
-      <c r="M46" s="22"/>
-      <c r="N46" s="20" t="s">
+      <c r="N46" s="22"/>
+      <c r="O46" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="O46" s="30" t="s">
+      <c r="P46" s="29" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="104.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16" ht="120" x14ac:dyDescent="0.2">
       <c r="A47" s="20" t="s">
         <v>202</v>
       </c>
       <c r="B47" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C47" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="C47" s="20" t="s">
+      <c r="D47" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="M47" s="22"/>
-      <c r="N47" s="20" t="s">
+      <c r="N47" s="22"/>
+      <c r="O47" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="O47" s="22" t="s">
+      <c r="P47" s="22" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="338.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16" ht="356" x14ac:dyDescent="0.2">
       <c r="A48" s="19" t="s">
         <v>207</v>
       </c>
       <c r="B48" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C48" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="C48" s="20" t="s">
+      <c r="D48" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="L48" s="22"/>
-      <c r="M48" s="22" t="s">
+      <c r="M48" s="22"/>
+      <c r="N48" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="N48" s="20" t="s">
+      <c r="O48" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="O48" s="22" t="s">
+      <c r="P48" s="22" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16" ht="60" x14ac:dyDescent="0.2">
       <c r="A49" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="B49" s="19" t="s">
+      <c r="B49" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C49" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="C49" s="20" t="s">
+      <c r="D49" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="D49" s="19">
+      <c r="E49" s="19">
         <v>1560</v>
       </c>
-      <c r="E49" s="19"/>
       <c r="F49" s="19"/>
       <c r="G49" s="19"/>
       <c r="H49" s="19"/>
       <c r="I49" s="19"/>
-      <c r="M49" s="22"/>
-    </row>
-    <row r="50" spans="1:15" ht="145" x14ac:dyDescent="0.35">
+      <c r="J49" s="19"/>
+      <c r="N49" s="22"/>
+    </row>
+    <row r="50" spans="1:16" ht="144" x14ac:dyDescent="0.2">
       <c r="A50" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="C50" s="19" t="s">
+      <c r="B50" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D50" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>1573</v>
       </c>
-      <c r="M50" s="22" t="s">
+      <c r="N50" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="N50" t="s">
+      <c r="O50" t="s">
         <v>219</v>
       </c>
-      <c r="O50" s="41" t="s">
+      <c r="P50" s="29" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:16" ht="45" x14ac:dyDescent="0.2">
       <c r="A51" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="C51" s="20" t="s">
+      <c r="B51" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D51" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19" t="s">
+      <c r="F51" s="19"/>
+      <c r="G51" s="19" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="65.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16" ht="75" x14ac:dyDescent="0.2">
       <c r="A52" s="19" t="s">
         <v>224</v>
       </c>
       <c r="B52" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C52" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="C52" s="20" t="s">
+      <c r="D52" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="D52" s="19">
+      <c r="E52" s="19">
         <v>1574</v>
       </c>
-      <c r="E52" s="19"/>
       <c r="F52" s="19"/>
-      <c r="H52" s="19"/>
-      <c r="L52" s="22" t="s">
+      <c r="G52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="M52" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="91.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:16" ht="105" x14ac:dyDescent="0.2">
       <c r="A53" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="C53" s="20" t="s">
+      <c r="B53" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D53" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="D53" s="19"/>
       <c r="E53" s="19"/>
       <c r="F53" s="19"/>
-      <c r="G53" s="19" t="s">
+      <c r="G53" s="19"/>
+      <c r="H53" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="H53" s="19"/>
-      <c r="M53" s="22" t="s">
+      <c r="I53" s="19"/>
+      <c r="N53" s="22" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="91.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:16" ht="105" x14ac:dyDescent="0.2">
       <c r="A54" s="20" t="s">
         <v>232</v>
       </c>
       <c r="B54" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C54" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="C54" s="20" t="s">
+      <c r="D54" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="D54" s="19">
+      <c r="E54" s="19">
         <v>1563</v>
       </c>
-      <c r="E54" s="19"/>
       <c r="F54" s="19"/>
-      <c r="H54" s="19"/>
-      <c r="L54" s="22" t="s">
+      <c r="G54" s="19"/>
+      <c r="I54" s="19"/>
+      <c r="M54" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="M54" s="22"/>
-      <c r="N54" s="19" t="s">
+      <c r="N54" s="22"/>
+      <c r="O54" s="19" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="104.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:16" ht="120" x14ac:dyDescent="0.2">
       <c r="A55" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="B55" s="20" t="s">
+      <c r="B55" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C55" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="C55" s="20" t="s">
+      <c r="D55" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="L55" s="22" t="s">
+      <c r="M55" s="22" t="s">
         <v>240</v>
       </c>
-      <c r="M55" s="22" t="s">
+      <c r="N55" s="22" t="s">
         <v>241</v>
       </c>
-      <c r="N55" s="20" t="s">
+      <c r="O55" s="20" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="91.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:16" ht="105" x14ac:dyDescent="0.2">
       <c r="A56" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="D56" s="19">
+      <c r="B56" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E56" s="19">
         <v>1604</v>
       </c>
-      <c r="E56" s="19"/>
       <c r="F56" s="19"/>
       <c r="G56" s="19"/>
-      <c r="H56">
+      <c r="H56" s="19"/>
+      <c r="I56">
         <v>1617</v>
       </c>
-      <c r="L56" s="22" t="s">
+      <c r="M56" s="22" t="s">
         <v>244</v>
       </c>
-      <c r="M56" s="22" t="s">
+      <c r="N56" s="22" t="s">
         <v>245</v>
       </c>
-      <c r="N56" s="20" t="s">
+      <c r="O56" s="20" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:16" ht="144" x14ac:dyDescent="0.2">
       <c r="A57" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="B57" s="20" t="s">
+      <c r="B57" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C57" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="C57" s="20" t="s">
+      <c r="D57" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="D57">
+      <c r="E57">
         <v>1563</v>
       </c>
-      <c r="L57" s="30" t="s">
+      <c r="M57" s="29" t="s">
         <v>250</v>
       </c>
-      <c r="M57" s="22"/>
-      <c r="N57" s="20" t="s">
+      <c r="N57" s="22"/>
+      <c r="O57" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="O57" s="30" t="s">
+      <c r="P57" s="29" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="116" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:16" ht="112" x14ac:dyDescent="0.2">
       <c r="A58" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="C58" s="20" t="s">
+      <c r="B58" s="24" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D58" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="D58">
+      <c r="E58">
         <v>1553</v>
       </c>
-      <c r="L58" s="30" t="s">
+      <c r="M58" s="29" t="s">
         <v>255</v>
       </c>
-      <c r="M58" s="22" t="s">
+      <c r="N58" s="22" t="s">
         <v>256</v>
       </c>
-      <c r="N58" t="s">
+      <c r="O58" t="s">
         <v>257</v>
       </c>
-      <c r="O58" s="30" t="s">
+      <c r="P58" s="29" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:16" ht="144" x14ac:dyDescent="0.2">
       <c r="A59" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C59" t="s">
         <v>260</v>
       </c>
-      <c r="C59" s="20" t="s">
+      <c r="D59" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="D59" s="19">
+      <c r="E59" s="19">
         <v>1566</v>
       </c>
-      <c r="E59" s="19"/>
       <c r="F59" s="19"/>
       <c r="G59" s="19"/>
       <c r="H59" s="19"/>
-      <c r="L59" s="30" t="s">
+      <c r="I59" s="19"/>
+      <c r="M59" s="29" t="s">
         <v>262</v>
       </c>
-      <c r="M59" s="22"/>
-      <c r="N59" t="s">
+      <c r="N59" s="22"/>
+      <c r="O59" t="s">
         <v>257</v>
       </c>
-      <c r="O59" s="30" t="s">
+      <c r="P59" s="29" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="143.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:16" ht="165" x14ac:dyDescent="0.2">
       <c r="A60" s="19" t="s">
         <v>264</v>
       </c>
       <c r="B60" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C60" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="C60" s="20" t="s">
+      <c r="D60" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="D60" s="19">
+      <c r="E60" s="19">
         <v>1543</v>
       </c>
-      <c r="E60" s="19"/>
       <c r="F60" s="19"/>
       <c r="G60" s="19"/>
       <c r="H60" s="19"/>
-      <c r="L60" s="22" t="s">
+      <c r="I60" s="19"/>
+      <c r="M60" s="22" t="s">
         <v>267</v>
       </c>
-      <c r="M60" s="22" t="s">
+      <c r="N60" s="22" t="s">
         <v>268</v>
       </c>
-      <c r="N60" s="19" t="s">
+      <c r="O60" s="19" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="65.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:16" ht="75" x14ac:dyDescent="0.2">
       <c r="A61" s="19" t="s">
         <v>270</v>
       </c>
       <c r="B61" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C61" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="C61" s="20" t="s">
+      <c r="D61" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="D61" s="19">
+      <c r="E61" s="19">
         <v>1573</v>
       </c>
-      <c r="H61" s="19"/>
-    </row>
-    <row r="62" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="I61" s="19"/>
+    </row>
+    <row r="62" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
         <v>273</v>
       </c>
-      <c r="C62" s="20" t="s">
+      <c r="B62" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D62" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="D62" s="19">
+      <c r="E62" s="19">
         <v>1574</v>
       </c>
-      <c r="E62" s="19"/>
       <c r="F62" s="19"/>
       <c r="G62" s="19"/>
       <c r="H62" s="19"/>
-      <c r="L62" s="22" t="s">
+      <c r="I62" s="19"/>
+      <c r="M62" s="22" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="91.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:16" ht="105" x14ac:dyDescent="0.2">
       <c r="A63" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="B63" s="19"/>
-      <c r="C63" s="20" t="s">
+      <c r="B63" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C63" s="19"/>
+      <c r="D63" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="L63" s="22" t="s">
+      <c r="M63" s="22" t="s">
         <v>278</v>
       </c>
-      <c r="M63" s="22" t="s">
+      <c r="N63" s="22" t="s">
         <v>279</v>
       </c>
-      <c r="N63" s="20" t="s">
+      <c r="O63" s="20" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="64" spans="1:15" s="21" customFormat="1" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:16" s="21" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A64" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="B64" s="19" t="s">
+      <c r="B64" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C64" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="C64" s="20" t="s">
+      <c r="D64" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="D64" s="19">
+      <c r="E64" s="19">
         <v>1578</v>
       </c>
-      <c r="E64" s="19"/>
       <c r="F64" s="19"/>
       <c r="G64" s="19"/>
       <c r="H64" s="19"/>
       <c r="I64" s="19"/>
       <c r="J64" s="19"/>
       <c r="K64" s="19"/>
-      <c r="L64" s="22"/>
-      <c r="M64" s="22" t="s">
+      <c r="L64" s="19"/>
+      <c r="M64" s="22"/>
+      <c r="N64" s="22" t="s">
         <v>284</v>
       </c>
-      <c r="N64" s="19"/>
-      <c r="O64" s="22" t="s">
+      <c r="O64" s="19"/>
+      <c r="P64" s="22" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="91.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:16" ht="90" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>286</v>
       </c>
       <c r="B65" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C65" t="s">
         <v>287</v>
       </c>
-      <c r="C65" s="20" t="s">
+      <c r="D65" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="D65">
+      <c r="E65">
         <v>1545</v>
       </c>
-      <c r="L65" s="22" t="s">
+      <c r="M65" s="22" t="s">
         <v>289</v>
       </c>
-      <c r="N65" t="s">
+      <c r="O65" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="91.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:16" ht="105" x14ac:dyDescent="0.2">
       <c r="A66" s="19" t="s">
         <v>291</v>
       </c>
       <c r="B66" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C66" s="19" t="s">
         <v>292</v>
       </c>
-      <c r="C66" s="20"/>
-      <c r="D66" s="19">
+      <c r="D66" s="20"/>
+      <c r="E66" s="19">
         <v>1569</v>
       </c>
-      <c r="E66" s="19"/>
       <c r="F66" s="19"/>
       <c r="G66" s="19"/>
       <c r="H66" s="19"/>
       <c r="I66" s="19"/>
       <c r="J66" s="19"/>
       <c r="K66" s="19"/>
-      <c r="L66" s="22" t="s">
+      <c r="L66" s="19"/>
+      <c r="M66" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="M66" s="22" t="s">
+      <c r="N66" s="22" t="s">
         <v>294</v>
       </c>
-      <c r="N66" s="19" t="s">
+      <c r="O66" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="O66" s="22" t="s">
+      <c r="P66" s="22" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A67" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="B67" s="20"/>
-      <c r="C67" s="20" t="s">
+      <c r="B67" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C67" s="20"/>
+      <c r="D67" s="20" t="s">
         <v>297</v>
       </c>
-      <c r="D67" s="19">
+      <c r="E67" s="19">
         <v>1574</v>
       </c>
-      <c r="E67" s="19"/>
       <c r="F67" s="19"/>
       <c r="G67" s="19"/>
-      <c r="H67" s="19">
+      <c r="H67" s="19"/>
+      <c r="I67" s="19">
         <v>1574</v>
       </c>
-      <c r="I67" s="19"/>
       <c r="J67" s="19"/>
       <c r="K67" s="19"/>
-      <c r="L67" s="22"/>
+      <c r="L67" s="19"/>
       <c r="M67" s="22"/>
-      <c r="N67" s="20" t="s">
+      <c r="N67" s="22"/>
+      <c r="O67" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="O67" s="22"/>
-    </row>
-    <row r="68" spans="1:15" ht="39.5" x14ac:dyDescent="0.35">
+      <c r="P67" s="22"/>
+    </row>
+    <row r="68" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A68" s="19" t="s">
         <v>298</v>
       </c>
       <c r="B68" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C68" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="C68" s="19" t="s">
+      <c r="D68" s="19" t="s">
         <v>300</v>
       </c>
-      <c r="D68" s="19"/>
       <c r="E68" s="19"/>
       <c r="F68" s="19"/>
       <c r="G68" s="19"/>
@@ -5788,190 +5993,211 @@
       <c r="I68" s="19"/>
       <c r="J68" s="19"/>
       <c r="K68" s="19"/>
-      <c r="L68" s="22" t="s">
+      <c r="L68" s="19"/>
+      <c r="M68" s="22" t="s">
         <v>301</v>
       </c>
-      <c r="M68" s="22"/>
-      <c r="N68" s="19"/>
-      <c r="O68" s="22"/>
-    </row>
-    <row r="69" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+      <c r="N68" s="22"/>
+      <c r="O68" s="19"/>
+      <c r="P68" s="22"/>
+    </row>
+    <row r="69" spans="1:16" ht="45" x14ac:dyDescent="0.2">
       <c r="A69" s="19" t="s">
         <v>302</v>
       </c>
       <c r="B69" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C69" s="19" t="s">
         <v>303</v>
       </c>
-      <c r="C69" s="22" t="s">
+      <c r="D69" s="22" t="s">
         <v>304</v>
       </c>
-      <c r="D69" s="19">
+      <c r="E69" s="19">
         <v>1553</v>
       </c>
-      <c r="E69" s="19"/>
       <c r="F69" s="19"/>
       <c r="G69" s="19"/>
       <c r="H69" s="19"/>
       <c r="I69" s="19"/>
       <c r="J69" s="19"/>
       <c r="K69" s="19"/>
-      <c r="L69" s="22" t="s">
+      <c r="L69" s="19"/>
+      <c r="M69" s="22" t="s">
         <v>305</v>
       </c>
-      <c r="M69" s="22"/>
-      <c r="N69" s="20" t="s">
+      <c r="N69" s="22"/>
+      <c r="O69" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="O69" s="22"/>
-    </row>
-    <row r="70" spans="1:15" ht="78.5" x14ac:dyDescent="0.35">
+      <c r="P69" s="22"/>
+    </row>
+    <row r="70" spans="1:16" ht="75" x14ac:dyDescent="0.2">
       <c r="A70" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="B70" s="19"/>
-      <c r="C70" s="20" t="s">
+      <c r="B70" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C70" s="19"/>
+      <c r="D70" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="D70" s="19">
+      <c r="E70" s="19">
         <v>1572</v>
       </c>
-      <c r="E70" s="19"/>
       <c r="F70" s="19"/>
       <c r="G70" s="19"/>
-      <c r="H70" s="19">
+      <c r="H70" s="19"/>
+      <c r="I70" s="19">
         <v>1622</v>
       </c>
-      <c r="I70" s="19"/>
       <c r="J70" s="19"/>
       <c r="K70" s="19"/>
-      <c r="L70" s="22" t="s">
+      <c r="L70" s="19"/>
+      <c r="M70" s="22" t="s">
         <v>309</v>
       </c>
-      <c r="M70" s="22"/>
-      <c r="N70" s="19"/>
-      <c r="O70" s="22" t="s">
+      <c r="N70" s="22"/>
+      <c r="O70" s="19"/>
+      <c r="P70" s="22" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="78.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:16" ht="75" x14ac:dyDescent="0.2">
       <c r="A71" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="B71" s="19"/>
-      <c r="C71" s="20" t="s">
+      <c r="B71" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C71" s="19"/>
+      <c r="D71" s="20" t="s">
         <v>312</v>
       </c>
-      <c r="D71" s="19">
+      <c r="E71" s="19">
         <v>1585</v>
       </c>
-      <c r="E71" s="19"/>
       <c r="F71" s="19"/>
       <c r="G71" s="19"/>
-      <c r="H71" s="19">
+      <c r="H71" s="19"/>
+      <c r="I71" s="19">
         <v>1621</v>
       </c>
-      <c r="I71" s="19"/>
       <c r="J71" s="19"/>
       <c r="K71" s="19"/>
-      <c r="L71" s="22" t="s">
+      <c r="L71" s="19"/>
+      <c r="M71" s="22" t="s">
         <v>313</v>
       </c>
-      <c r="M71" s="22"/>
-      <c r="N71" s="19"/>
-      <c r="O71" s="22"/>
-    </row>
-    <row r="72" spans="1:15" ht="91.5" x14ac:dyDescent="0.35">
+      <c r="N71" s="22"/>
+      <c r="O71" s="19"/>
+      <c r="P71" s="22"/>
+    </row>
+    <row r="72" spans="1:16" ht="90" x14ac:dyDescent="0.2">
       <c r="A72" s="19" t="s">
         <v>314</v>
       </c>
-      <c r="B72" s="19"/>
-      <c r="C72" s="20" t="s">
+      <c r="B72" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C72" s="19"/>
+      <c r="D72" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="D72" s="19"/>
-      <c r="E72" s="19">
+      <c r="E72" s="19"/>
+      <c r="F72" s="19">
         <v>1580</v>
       </c>
-      <c r="F72" s="19"/>
       <c r="G72" s="19"/>
-      <c r="H72" s="19">
+      <c r="H72" s="19"/>
+      <c r="I72" s="19">
         <v>1662</v>
       </c>
-      <c r="I72" s="19"/>
       <c r="J72" s="19"/>
       <c r="K72" s="19"/>
-      <c r="L72" s="22" t="s">
+      <c r="L72" s="19"/>
+      <c r="M72" s="22" t="s">
         <v>316</v>
       </c>
-      <c r="M72" s="22"/>
-      <c r="N72" s="19"/>
-      <c r="O72" s="22" t="s">
+      <c r="N72" s="22"/>
+      <c r="O72" s="19"/>
+      <c r="P72" s="22" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:16" ht="60" x14ac:dyDescent="0.2">
       <c r="A73" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="B73" s="19"/>
-      <c r="C73" s="20" t="s">
+      <c r="B73" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="D73" s="19">
+      <c r="E73" s="19">
         <v>1519</v>
       </c>
-      <c r="E73" s="19"/>
       <c r="F73" s="19"/>
       <c r="G73" s="19"/>
-      <c r="H73" s="19">
+      <c r="H73" s="19"/>
+      <c r="I73" s="19">
         <v>1585</v>
       </c>
-      <c r="I73" s="19"/>
       <c r="J73" s="19"/>
       <c r="K73" s="19"/>
-      <c r="L73" s="22"/>
-      <c r="M73" s="22" t="s">
+      <c r="L73" s="19"/>
+      <c r="M73" s="22"/>
+      <c r="N73" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="N73" s="19"/>
-      <c r="O73" s="22"/>
-    </row>
-    <row r="74" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="O73" s="19"/>
+      <c r="P73" s="22"/>
+    </row>
+    <row r="74" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A74" s="19" t="s">
         <v>321</v>
       </c>
-      <c r="B74" s="19"/>
-      <c r="C74" s="20" t="s">
+      <c r="B74" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C74" s="19"/>
+      <c r="D74" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="D74" s="19"/>
       <c r="E74" s="19"/>
       <c r="F74" s="19"/>
       <c r="G74" s="19"/>
-      <c r="H74" s="19">
+      <c r="H74" s="19"/>
+      <c r="I74" s="19">
         <v>1622</v>
       </c>
-      <c r="I74" s="19"/>
       <c r="J74" s="19"/>
       <c r="K74" s="19"/>
-      <c r="L74" s="22"/>
-      <c r="M74" s="22" t="s">
+      <c r="L74" s="19"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22" t="s">
         <v>323</v>
       </c>
-      <c r="N74" s="19"/>
-      <c r="O74" s="22" t="s">
+      <c r="O74" s="19"/>
+      <c r="P74" s="22" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75" s="19" t="s">
         <v>325</v>
       </c>
-      <c r="B75" s="19"/>
-      <c r="C75" s="20" t="s">
+      <c r="B75" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C75" s="19"/>
+      <c r="D75" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="D75" s="19"/>
       <c r="E75" s="19"/>
       <c r="F75" s="19"/>
       <c r="G75" s="19"/>
@@ -5979,88 +6205,100 @@
       <c r="I75" s="19"/>
       <c r="J75" s="19"/>
       <c r="K75" s="19"/>
-      <c r="L75" s="22"/>
+      <c r="L75" s="19"/>
       <c r="M75" s="22"/>
-      <c r="N75" s="19"/>
-      <c r="O75" s="22"/>
-    </row>
-    <row r="76" spans="1:15" ht="39.5" x14ac:dyDescent="0.35">
+      <c r="N75" s="22"/>
+      <c r="O75" s="19"/>
+      <c r="P75" s="22"/>
+    </row>
+    <row r="76" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A76" s="19" t="s">
         <v>327</v>
       </c>
-      <c r="B76" s="19"/>
-      <c r="C76" s="20" t="s">
+      <c r="B76" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C76" s="19"/>
+      <c r="D76" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="D76" s="19"/>
       <c r="E76" s="19"/>
       <c r="F76" s="19"/>
       <c r="G76" s="19"/>
-      <c r="H76" s="19">
+      <c r="H76" s="19"/>
+      <c r="I76" s="19">
         <v>1664</v>
       </c>
-      <c r="I76" s="19"/>
       <c r="J76" s="19"/>
       <c r="K76" s="19"/>
-      <c r="L76" s="22" t="s">
+      <c r="L76" s="19"/>
+      <c r="M76" s="22" t="s">
         <v>328</v>
       </c>
-      <c r="M76" s="22"/>
-      <c r="N76" s="19"/>
-      <c r="O76" s="22"/>
-    </row>
-    <row r="77" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+      <c r="N76" s="22"/>
+      <c r="O76" s="19"/>
+      <c r="P76" s="22"/>
+    </row>
+    <row r="77" spans="1:16" ht="60" x14ac:dyDescent="0.2">
       <c r="A77" s="19" t="s">
         <v>329</v>
       </c>
-      <c r="B77" s="19"/>
-      <c r="C77" s="19" t="s">
+      <c r="B77" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="D77" s="19">
+      <c r="E77" s="19">
         <v>1539</v>
       </c>
-      <c r="E77" s="19"/>
       <c r="F77" s="19"/>
       <c r="G77" s="19"/>
-      <c r="H77" s="19">
+      <c r="H77" s="19"/>
+      <c r="I77" s="19">
         <v>1610</v>
       </c>
-      <c r="I77" s="19"/>
-      <c r="L77" s="22" t="s">
+      <c r="J77" s="19"/>
+      <c r="M77" s="22" t="s">
         <v>331</v>
       </c>
-      <c r="M77" s="22" t="s">
+      <c r="N77" s="22" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="65.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:16" ht="75" x14ac:dyDescent="0.2">
       <c r="A78" s="19" t="s">
         <v>333</v>
       </c>
-      <c r="B78" s="19"/>
-      <c r="C78" s="20" t="s">
+      <c r="B78" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C78" s="19"/>
+      <c r="D78" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="D78" s="19">
+      <c r="E78" s="19">
         <v>1575</v>
       </c>
-      <c r="L78" s="22" t="s">
+      <c r="M78" s="22" t="s">
         <v>335</v>
       </c>
-      <c r="M78" s="22" t="s">
+      <c r="N78" s="22" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79" s="19" t="s">
         <v>336</v>
       </c>
-      <c r="B79" s="19"/>
-      <c r="C79" s="19" t="s">
+      <c r="B79" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C79" s="19"/>
+      <c r="D79" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="D79" s="19"/>
       <c r="E79" s="19"/>
       <c r="F79" s="19"/>
       <c r="G79" s="19"/>
@@ -6068,402 +6306,465 @@
       <c r="I79" s="19"/>
       <c r="J79" s="19"/>
       <c r="K79" s="19"/>
-      <c r="L79" s="22"/>
+      <c r="L79" s="19"/>
       <c r="M79" s="22"/>
-      <c r="N79" s="19" t="s">
+      <c r="N79" s="22"/>
+      <c r="O79" s="19" t="s">
         <v>280</v>
       </c>
-      <c r="O79" s="22"/>
-    </row>
-    <row r="80" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="P79" s="22"/>
+    </row>
+    <row r="80" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A80" s="19" t="s">
         <v>338</v>
       </c>
       <c r="B80" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C80" s="19" t="s">
         <v>339</v>
       </c>
-      <c r="C80" s="20" t="s">
+      <c r="D80" s="20" t="s">
         <v>340</v>
       </c>
-      <c r="D80" s="19">
+      <c r="E80" s="19">
         <v>1593</v>
       </c>
-      <c r="E80" s="19"/>
       <c r="F80" s="19"/>
       <c r="G80" s="19"/>
-      <c r="H80" s="19">
+      <c r="H80" s="19"/>
+      <c r="I80" s="19">
         <v>1625</v>
       </c>
-      <c r="L80" s="22" t="s">
+      <c r="M80" s="22" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="81" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:16" ht="60" x14ac:dyDescent="0.2">
       <c r="A81" s="19" t="s">
         <v>342</v>
       </c>
       <c r="B81" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C81" s="19" t="s">
         <v>343</v>
       </c>
-      <c r="C81" s="20" t="s">
+      <c r="D81" s="20" t="s">
         <v>344</v>
       </c>
-      <c r="D81" s="19">
+      <c r="E81" s="19">
         <v>1578</v>
       </c>
-      <c r="E81" s="19"/>
       <c r="F81" s="19"/>
       <c r="G81" s="19"/>
-      <c r="H81" s="19">
+      <c r="H81" s="19"/>
+      <c r="I81" s="19">
         <v>1653</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82" s="19" t="s">
         <v>345</v>
       </c>
       <c r="B82" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C82" s="19" t="s">
         <v>346</v>
       </c>
-      <c r="C82" s="19" t="s">
+      <c r="D82" s="19" t="s">
         <v>347</v>
       </c>
-      <c r="D82" s="19">
+      <c r="E82" s="19">
         <v>1558</v>
       </c>
-      <c r="E82" s="19"/>
       <c r="F82" s="19"/>
       <c r="G82" s="19"/>
-      <c r="H82" s="19">
+      <c r="H82" s="19"/>
+      <c r="I82" s="19">
         <v>1645</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="91.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:16" ht="105" x14ac:dyDescent="0.2">
       <c r="A83" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="B83" s="20" t="s">
+      <c r="B83" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C83" s="20" t="s">
         <v>349</v>
       </c>
-      <c r="C83" s="20" t="s">
+      <c r="D83" s="20" t="s">
         <v>350</v>
       </c>
-      <c r="L83" s="22" t="s">
+      <c r="M83" s="22" t="s">
         <v>351</v>
       </c>
-      <c r="M83" s="22" t="s">
+      <c r="N83" s="22" t="s">
         <v>352</v>
       </c>
-      <c r="N83" s="20" t="s">
+      <c r="O83" s="20" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:16" ht="45" x14ac:dyDescent="0.2">
       <c r="A84" s="20" t="s">
         <v>354</v>
       </c>
       <c r="B84" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C84" s="20" t="s">
         <v>355</v>
       </c>
-      <c r="C84" s="24" t="s">
+      <c r="D84" s="24" t="s">
         <v>356</v>
       </c>
-      <c r="L84" s="39" t="s">
+      <c r="M84" s="35" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="85" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:16" ht="45" x14ac:dyDescent="0.2">
       <c r="A85" s="20" t="s">
         <v>358</v>
       </c>
-      <c r="C85" s="24" t="s">
+      <c r="B85" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D85" s="24" t="s">
         <v>356</v>
       </c>
-      <c r="L85" s="39" t="s">
+      <c r="M85" s="35" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="86" spans="1:15" ht="78.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:16" ht="90" x14ac:dyDescent="0.2">
       <c r="A86" s="20" t="s">
         <v>359</v>
       </c>
-      <c r="C86" s="20" t="s">
+      <c r="B86" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D86" s="20" t="s">
         <v>360</v>
       </c>
-      <c r="L86" s="40" t="s">
+      <c r="M86" s="36" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="87" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:16" ht="60" x14ac:dyDescent="0.2">
       <c r="A87" s="20" t="s">
         <v>362</v>
       </c>
       <c r="B87" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C87" s="20" t="s">
         <v>363</v>
       </c>
-      <c r="C87" s="20" t="s">
+      <c r="D87" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="L87" s="22" t="s">
+      <c r="M87" s="22" t="s">
         <v>365</v>
       </c>
-      <c r="N87" s="20" t="s">
+      <c r="O87" s="20" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="88" spans="1:15" ht="377" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:16" ht="365" x14ac:dyDescent="0.2">
       <c r="A88" s="19" t="s">
         <v>366</v>
       </c>
       <c r="B88" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C88" s="19" t="s">
         <v>367</v>
       </c>
-      <c r="C88" s="27" t="s">
+      <c r="D88" s="27" t="s">
         <v>368</v>
       </c>
-      <c r="L88" s="22" t="s">
+      <c r="M88" s="22" t="s">
         <v>369</v>
       </c>
-      <c r="N88" s="20" t="s">
+      <c r="O88" s="20" t="s">
         <v>370</v>
       </c>
-      <c r="O88" s="30" t="s">
+      <c r="P88" s="29" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="89" spans="1:15" ht="78.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:16" ht="75" x14ac:dyDescent="0.2">
       <c r="A89" s="20" t="s">
         <v>372</v>
       </c>
       <c r="B89" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C89" s="20" t="s">
         <v>373</v>
       </c>
-      <c r="C89" s="20" t="s">
+      <c r="D89" s="20" t="s">
         <v>374</v>
       </c>
-      <c r="L89" s="22" t="s">
+      <c r="M89" s="22" t="s">
         <v>375</v>
       </c>
-      <c r="N89" s="20" t="s">
+      <c r="O89" s="20" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="90" spans="1:15" ht="78.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:16" ht="90" x14ac:dyDescent="0.2">
       <c r="A90" s="20" t="s">
         <v>377</v>
       </c>
       <c r="B90" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C90" s="20" t="s">
         <v>378</v>
       </c>
-      <c r="C90" s="20" t="s">
+      <c r="D90" s="20" t="s">
         <v>379</v>
       </c>
-      <c r="L90" s="40" t="s">
+      <c r="M90" s="36" t="s">
         <v>380</v>
       </c>
-      <c r="N90" s="20" t="s">
+      <c r="O90" s="20" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="91" spans="1:15" ht="83.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16" ht="83.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="19" t="s">
         <v>381</v>
       </c>
-      <c r="C91" s="20" t="s">
+      <c r="B91" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D91" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="D91" s="19">
+      <c r="E91" s="19">
         <v>1567</v>
       </c>
-      <c r="E91" s="19"/>
       <c r="F91" s="19"/>
       <c r="G91" s="19"/>
-      <c r="H91" s="19">
+      <c r="H91" s="19"/>
+      <c r="I91" s="19">
         <v>1626</v>
       </c>
-      <c r="N91" s="20" t="s">
+      <c r="O91" s="20" t="s">
         <v>383</v>
       </c>
-      <c r="O91" s="22" t="s">
+      <c r="P91" s="22" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="92" spans="1:15" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:16" ht="45" x14ac:dyDescent="0.2">
       <c r="A92" s="19" t="s">
         <v>385</v>
       </c>
       <c r="B92" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C92" s="19" t="s">
         <v>386</v>
       </c>
-      <c r="C92" s="20" t="s">
+      <c r="D92" s="20" t="s">
         <v>387</v>
       </c>
-      <c r="D92" s="19">
+      <c r="E92" s="19">
         <v>1583</v>
       </c>
-      <c r="E92" s="19"/>
       <c r="F92" s="19"/>
       <c r="G92" s="19"/>
-      <c r="H92" s="19">
+      <c r="H92" s="19"/>
+      <c r="I92" s="19">
         <v>1667</v>
       </c>
-      <c r="N92" s="19" t="s">
+      <c r="O92" s="19" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="93" spans="1:15" ht="91.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:16" ht="105" x14ac:dyDescent="0.2">
       <c r="A93" s="19" t="s">
         <v>388</v>
       </c>
       <c r="B93" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C93" s="19" t="s">
         <v>389</v>
       </c>
-      <c r="C93" s="20" t="s">
+      <c r="D93" s="20" t="s">
         <v>390</v>
       </c>
-      <c r="N93" s="20" t="s">
+      <c r="O93" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="O93" s="30" t="s">
+      <c r="P93" s="29" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="94" spans="1:15" ht="116" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:16" ht="112" x14ac:dyDescent="0.2">
       <c r="A94" s="19" t="s">
         <v>393</v>
       </c>
       <c r="B94" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C94" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="C94" s="20" t="s">
+      <c r="D94" s="20" t="s">
         <v>395</v>
       </c>
-      <c r="N94" s="20" t="s">
+      <c r="O94" s="20" t="s">
         <v>396</v>
       </c>
-      <c r="O94" s="41" t="s">
+      <c r="P94" s="29" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="95" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A95" s="19" t="s">
         <v>398</v>
       </c>
       <c r="B95" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C95" s="19" t="s">
         <v>399</v>
       </c>
-      <c r="C95" s="20" t="s">
+      <c r="D95" s="20" t="s">
         <v>400</v>
       </c>
-      <c r="N95" s="19" t="s">
+      <c r="O95" s="19" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="96" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:16" ht="64" x14ac:dyDescent="0.2">
       <c r="A96" s="19" t="s">
         <v>401</v>
       </c>
-      <c r="B96" s="19"/>
-      <c r="C96" s="19" t="s">
+      <c r="B96" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C96" s="19"/>
+      <c r="D96" s="19" t="s">
         <v>402</v>
       </c>
-      <c r="N96" s="19" t="s">
+      <c r="O96" s="19" t="s">
         <v>403</v>
       </c>
-      <c r="O96" s="41" t="s">
+      <c r="P96" s="29" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="117.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:16" ht="135" x14ac:dyDescent="0.2">
       <c r="A97" s="19" t="s">
         <v>405</v>
       </c>
       <c r="B97" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C97" s="19" t="s">
         <v>406</v>
       </c>
-      <c r="C97" s="20" t="s">
+      <c r="D97" s="20" t="s">
         <v>407</v>
       </c>
-      <c r="H97" s="19">
+      <c r="I97" s="19">
         <v>1619</v>
       </c>
-      <c r="L97" s="22"/>
-      <c r="N97" s="20" t="s">
+      <c r="M97" s="22"/>
+      <c r="O97" s="20" t="s">
         <v>408</v>
       </c>
-      <c r="O97" s="22" t="s">
+      <c r="P97" s="22" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="351.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:16" ht="342" x14ac:dyDescent="0.2">
       <c r="A98" s="19" t="s">
         <v>410</v>
       </c>
       <c r="B98" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C98" s="19" t="s">
         <v>411</v>
       </c>
-      <c r="C98" s="20" t="s">
+      <c r="D98" s="20" t="s">
         <v>412</v>
       </c>
-      <c r="D98" s="19">
+      <c r="E98" s="19">
         <v>1573</v>
       </c>
-      <c r="E98" s="19"/>
       <c r="F98" s="19"/>
       <c r="G98" s="19"/>
-      <c r="H98" s="19">
+      <c r="H98" s="19"/>
+      <c r="I98" s="19">
         <v>1660</v>
       </c>
-      <c r="L98" s="22" t="s">
+      <c r="M98" s="22" t="s">
         <v>413</v>
       </c>
-      <c r="N98" s="20" t="s">
+      <c r="O98" s="20" t="s">
         <v>414</v>
       </c>
-      <c r="O98" s="22" t="s">
+      <c r="P98" s="22" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="99" spans="1:15" ht="104.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:16" ht="120" x14ac:dyDescent="0.2">
       <c r="A99" s="19" t="s">
         <v>416</v>
       </c>
-      <c r="B99" s="27" t="s">
+      <c r="B99" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C99" s="27" t="s">
         <v>417</v>
       </c>
-      <c r="C99" s="27" t="s">
+      <c r="D99" s="27" t="s">
         <v>418</v>
       </c>
-      <c r="D99" s="19">
+      <c r="E99" s="19">
         <v>1553</v>
       </c>
-      <c r="E99" s="19"/>
       <c r="F99" s="19"/>
       <c r="G99" s="19"/>
-      <c r="H99" s="19">
+      <c r="H99" s="19"/>
+      <c r="I99" s="19">
         <v>1619</v>
       </c>
-      <c r="L99" s="40" t="s">
+      <c r="M99" s="36" t="s">
         <v>419</v>
       </c>
-      <c r="N99" t="s">
+      <c r="O99" t="s">
         <v>420</v>
       </c>
-      <c r="O99" s="22" t="s">
+      <c r="P99" s="22" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="100" spans="1:15" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:16" ht="150" x14ac:dyDescent="0.2">
       <c r="A100" s="19" t="s">
         <v>422</v>
       </c>
       <c r="B100" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C100" s="19" t="s">
         <v>423</v>
       </c>
-      <c r="C100" s="19" t="s">
+      <c r="D100" s="19" t="s">
         <v>424</v>
       </c>
-      <c r="D100" s="19"/>
       <c r="E100" s="19"/>
       <c r="F100" s="19"/>
       <c r="G100" s="19"/>
@@ -6471,26 +6772,29 @@
       <c r="I100" s="19"/>
       <c r="J100" s="19"/>
       <c r="K100" s="19"/>
-      <c r="L100" s="22" t="s">
+      <c r="L100" s="19"/>
+      <c r="M100" s="22" t="s">
         <v>425</v>
       </c>
-      <c r="M100" s="22"/>
-      <c r="N100" s="19" t="s">
+      <c r="N100" s="22"/>
+      <c r="O100" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="O100" s="22" t="s">
+      <c r="P100" s="22" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="101" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A101" s="19" t="s">
         <v>427</v>
       </c>
-      <c r="B101" s="19"/>
-      <c r="C101" s="20" t="s">
+      <c r="B101" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C101" s="19"/>
+      <c r="D101" s="20" t="s">
         <v>428</v>
       </c>
-      <c r="D101" s="19"/>
       <c r="E101" s="19"/>
       <c r="F101" s="19"/>
       <c r="G101" s="19"/>
@@ -6498,18 +6802,21 @@
       <c r="I101" s="19"/>
       <c r="J101" s="19"/>
       <c r="K101" s="19"/>
-      <c r="L101" s="22"/>
+      <c r="L101" s="19"/>
       <c r="M101" s="22"/>
-      <c r="N101" s="19"/>
-    </row>
-    <row r="102" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+      <c r="N101" s="22"/>
+      <c r="O101" s="19"/>
+    </row>
+    <row r="102" spans="1:16" ht="60" x14ac:dyDescent="0.2">
       <c r="A102" s="19" t="s">
         <v>429</v>
       </c>
       <c r="B102" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C102" s="19" t="s">
         <v>430</v>
       </c>
-      <c r="C102" s="19"/>
       <c r="D102" s="19"/>
       <c r="E102" s="19"/>
       <c r="F102" s="19"/>
@@ -6518,23 +6825,26 @@
       <c r="I102" s="19"/>
       <c r="J102" s="19"/>
       <c r="K102" s="19"/>
-      <c r="L102" s="22" t="s">
+      <c r="L102" s="19"/>
+      <c r="M102" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="M102" s="22" t="s">
+      <c r="N102" s="22" t="s">
         <v>432</v>
       </c>
-      <c r="N102" s="19"/>
-    </row>
-    <row r="103" spans="1:15" ht="39.5" x14ac:dyDescent="0.35">
+      <c r="O102" s="19"/>
+    </row>
+    <row r="103" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A103" s="19" t="s">
         <v>433</v>
       </c>
-      <c r="B103" s="19"/>
-      <c r="C103" s="20" t="s">
+      <c r="B103" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C103" s="19"/>
+      <c r="D103" s="20" t="s">
         <v>434</v>
       </c>
-      <c r="D103" s="19"/>
       <c r="E103" s="19"/>
       <c r="F103" s="19"/>
       <c r="G103" s="19"/>
@@ -6542,23 +6852,26 @@
       <c r="I103" s="19"/>
       <c r="J103" s="19"/>
       <c r="K103" s="19"/>
-      <c r="L103" s="22"/>
+      <c r="L103" s="19"/>
       <c r="M103" s="22"/>
-      <c r="N103" s="20" t="s">
+      <c r="N103" s="22"/>
+      <c r="O103" s="20" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="104" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:16" ht="45" x14ac:dyDescent="0.2">
       <c r="A104" s="19" t="s">
         <v>436</v>
       </c>
       <c r="B104" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C104" s="19" t="s">
         <v>437</v>
       </c>
-      <c r="C104" s="20" t="s">
+      <c r="D104" s="20" t="s">
         <v>438</v>
       </c>
-      <c r="D104" s="19"/>
       <c r="E104" s="19"/>
       <c r="F104" s="19"/>
       <c r="G104" s="19"/>
@@ -6566,21 +6879,24 @@
       <c r="I104" s="19"/>
       <c r="J104" s="19"/>
       <c r="K104" s="19"/>
-      <c r="L104" s="22"/>
+      <c r="L104" s="19"/>
       <c r="M104" s="22"/>
-      <c r="N104" s="20" t="s">
+      <c r="N104" s="22"/>
+      <c r="O104" s="20" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="105" spans="1:15" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:16" ht="45" x14ac:dyDescent="0.2">
       <c r="A105" s="19" t="s">
         <v>440</v>
       </c>
-      <c r="B105" s="19"/>
-      <c r="C105" s="20" t="s">
+      <c r="B105" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C105" s="19"/>
+      <c r="D105" s="20" t="s">
         <v>441</v>
       </c>
-      <c r="D105" s="19"/>
       <c r="E105" s="19"/>
       <c r="F105" s="19"/>
       <c r="G105" s="19"/>
@@ -6588,23 +6904,26 @@
       <c r="I105" s="19"/>
       <c r="J105" s="19"/>
       <c r="K105" s="19"/>
-      <c r="L105" s="22"/>
+      <c r="L105" s="19"/>
       <c r="M105" s="22"/>
-      <c r="N105" s="20" t="s">
+      <c r="N105" s="22"/>
+      <c r="O105" s="20" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="106" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A106" s="19" t="s">
         <v>442</v>
       </c>
       <c r="B106" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C106" s="19" t="s">
         <v>443</v>
       </c>
-      <c r="C106" s="22" t="s">
+      <c r="D106" s="22" t="s">
         <v>444</v>
       </c>
-      <c r="D106" s="19"/>
       <c r="E106" s="19"/>
       <c r="F106" s="19"/>
       <c r="G106" s="19"/>
@@ -6612,19 +6931,22 @@
       <c r="I106" s="19"/>
       <c r="J106" s="19"/>
       <c r="K106" s="19"/>
-      <c r="L106" s="22"/>
+      <c r="L106" s="19"/>
       <c r="M106" s="22"/>
-      <c r="N106" s="19"/>
-    </row>
-    <row r="107" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="N106" s="22"/>
+      <c r="O106" s="19"/>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A107" s="19" t="s">
         <v>445</v>
       </c>
-      <c r="B107" s="19"/>
-      <c r="C107" s="22" t="s">
+      <c r="B107" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C107" s="19"/>
+      <c r="D107" s="22" t="s">
         <v>444</v>
       </c>
-      <c r="D107" s="19"/>
       <c r="E107" s="19"/>
       <c r="F107" s="19"/>
       <c r="G107" s="19"/>
@@ -6632,19 +6954,22 @@
       <c r="I107" s="19"/>
       <c r="J107" s="19"/>
       <c r="K107" s="19"/>
-      <c r="L107" s="22"/>
+      <c r="L107" s="19"/>
       <c r="M107" s="22"/>
-      <c r="N107" s="19"/>
-    </row>
-    <row r="108" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="N107" s="22"/>
+      <c r="O107" s="19"/>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A108" s="19" t="s">
         <v>446</v>
       </c>
-      <c r="B108" s="19"/>
-      <c r="C108" s="22" t="s">
+      <c r="B108" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C108" s="19"/>
+      <c r="D108" s="22" t="s">
         <v>444</v>
       </c>
-      <c r="D108" s="19"/>
       <c r="E108" s="19"/>
       <c r="F108" s="19"/>
       <c r="G108" s="19"/>
@@ -6652,61 +6977,70 @@
       <c r="I108" s="19"/>
       <c r="J108" s="19"/>
       <c r="K108" s="19"/>
-      <c r="L108" s="22"/>
+      <c r="L108" s="19"/>
       <c r="M108" s="22"/>
-      <c r="N108" s="19"/>
-    </row>
-    <row r="109" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+      <c r="N108" s="22"/>
+      <c r="O108" s="19"/>
+    </row>
+    <row r="109" spans="1:16" ht="60" x14ac:dyDescent="0.2">
       <c r="A109" s="19" t="s">
         <v>447</v>
       </c>
-      <c r="C109" s="26" t="s">
+      <c r="B109" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D109" s="26" t="s">
         <v>448</v>
       </c>
-      <c r="H109">
+      <c r="I109">
         <v>1631</v>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:16" ht="96" x14ac:dyDescent="0.2">
       <c r="A110" s="19" t="s">
         <v>449</v>
       </c>
       <c r="B110" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C110" s="19" t="s">
         <v>450</v>
       </c>
-      <c r="C110" s="22" t="s">
+      <c r="D110" s="22" t="s">
         <v>451</v>
       </c>
-      <c r="D110" s="19">
+      <c r="E110" s="19">
         <v>1589</v>
       </c>
-      <c r="E110" s="19"/>
       <c r="F110" s="19"/>
       <c r="G110" s="19"/>
-      <c r="H110" s="19">
+      <c r="H110" s="19"/>
+      <c r="I110" s="19">
         <v>1648</v>
       </c>
-      <c r="I110" s="19"/>
       <c r="J110" s="19"/>
       <c r="K110" s="19"/>
-      <c r="L110" s="22" t="s">
+      <c r="L110" s="19"/>
+      <c r="M110" s="22" t="s">
         <v>452</v>
       </c>
-      <c r="O110" s="41" t="s">
+      <c r="P110" s="29" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="111" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:16" ht="64" x14ac:dyDescent="0.2">
       <c r="A111" s="19" t="s">
         <v>454</v>
       </c>
       <c r="B111" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C111" s="19" t="s">
         <v>455</v>
       </c>
-      <c r="C111" s="19" t="s">
+      <c r="D111" s="19" t="s">
         <v>456</v>
       </c>
-      <c r="D111" s="19"/>
       <c r="E111" s="19"/>
       <c r="F111" s="19"/>
       <c r="G111" s="19"/>
@@ -6714,51 +7048,57 @@
       <c r="I111" s="19"/>
       <c r="J111" s="19"/>
       <c r="K111" s="19"/>
-      <c r="L111" s="22" t="s">
+      <c r="L111" s="19"/>
+      <c r="M111" s="22" t="s">
         <v>457</v>
       </c>
-      <c r="O111" s="41" t="s">
+      <c r="P111" s="29" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="112" spans="1:15" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:16" ht="96" x14ac:dyDescent="0.2">
       <c r="A112" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="B112" s="19" t="s">
+      <c r="B112" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C112" s="19" t="s">
         <v>460</v>
       </c>
-      <c r="C112" s="19" t="s">
+      <c r="D112" s="19" t="s">
         <v>461</v>
       </c>
-      <c r="D112" s="19">
+      <c r="E112" s="19">
         <v>1574</v>
       </c>
-      <c r="E112" s="19"/>
       <c r="F112" s="19"/>
       <c r="G112" s="19"/>
-      <c r="H112" s="19">
+      <c r="H112" s="19"/>
+      <c r="I112" s="19">
         <v>1617</v>
       </c>
-      <c r="I112" s="19"/>
       <c r="J112" s="19"/>
       <c r="K112" s="19"/>
-      <c r="L112" s="22" t="s">
+      <c r="L112" s="19"/>
+      <c r="M112" s="22" t="s">
         <v>462</v>
       </c>
-      <c r="O112" s="41" t="s">
+      <c r="P112" s="29" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="113" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:17" ht="64" x14ac:dyDescent="0.2">
       <c r="A113" s="19" t="s">
         <v>464</v>
       </c>
-      <c r="B113" s="19"/>
-      <c r="C113" s="19" t="s">
+      <c r="B113" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C113" s="19"/>
+      <c r="D113" s="19" t="s">
         <v>465</v>
       </c>
-      <c r="D113" s="19"/>
       <c r="E113" s="19"/>
       <c r="F113" s="19"/>
       <c r="G113" s="19"/>
@@ -6766,22 +7106,25 @@
       <c r="I113" s="19"/>
       <c r="J113" s="19"/>
       <c r="K113" s="19"/>
-      <c r="L113" s="22" t="s">
+      <c r="L113" s="19"/>
+      <c r="M113" s="22" t="s">
         <v>466</v>
       </c>
-      <c r="O113" s="41" t="s">
+      <c r="P113" s="29" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="114" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:17" ht="64" x14ac:dyDescent="0.2">
       <c r="A114" s="19" t="s">
         <v>467</v>
       </c>
-      <c r="B114" s="19"/>
-      <c r="C114" s="19" t="s">
+      <c r="B114" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C114" s="19"/>
+      <c r="D114" s="19" t="s">
         <v>468</v>
       </c>
-      <c r="D114" s="19"/>
       <c r="E114" s="19"/>
       <c r="F114" s="19"/>
       <c r="G114" s="19"/>
@@ -6789,22 +7132,25 @@
       <c r="I114" s="19"/>
       <c r="J114" s="19"/>
       <c r="K114" s="19"/>
-      <c r="L114" s="22" t="s">
+      <c r="L114" s="19"/>
+      <c r="M114" s="22" t="s">
         <v>469</v>
       </c>
-      <c r="O114" s="41" t="s">
+      <c r="P114" s="29" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="115" spans="1:16" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:17" ht="30" x14ac:dyDescent="0.2">
       <c r="A115" s="19" t="s">
         <v>470</v>
       </c>
-      <c r="B115" s="19"/>
-      <c r="C115" s="19" t="s">
+      <c r="B115" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C115" s="19"/>
+      <c r="D115" s="19" t="s">
         <v>471</v>
       </c>
-      <c r="D115" s="19"/>
       <c r="E115" s="19"/>
       <c r="F115" s="19"/>
       <c r="G115" s="19"/>
@@ -6812,19 +7158,22 @@
       <c r="I115" s="19"/>
       <c r="J115" s="19"/>
       <c r="K115" s="19"/>
-      <c r="L115" s="22" t="s">
+      <c r="L115" s="19"/>
+      <c r="M115" s="22" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A116" s="19" t="s">
         <v>473</v>
       </c>
-      <c r="B116" s="19"/>
-      <c r="C116" s="19" t="s">
+      <c r="B116" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C116" s="19"/>
+      <c r="D116" s="19" t="s">
         <v>474</v>
       </c>
-      <c r="D116" s="19"/>
       <c r="E116" s="19"/>
       <c r="F116" s="19"/>
       <c r="G116" s="19"/>
@@ -6832,17 +7181,20 @@
       <c r="I116" s="19"/>
       <c r="J116" s="19"/>
       <c r="K116" s="19"/>
-      <c r="L116" s="22"/>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="L116" s="19"/>
+      <c r="M116" s="22"/>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A117" s="19" t="s">
         <v>475</v>
       </c>
-      <c r="B117" s="19"/>
-      <c r="C117" s="19" t="s">
+      <c r="B117" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C117" s="19"/>
+      <c r="D117" s="19" t="s">
         <v>476</v>
       </c>
-      <c r="D117" s="19"/>
       <c r="E117" s="19"/>
       <c r="F117" s="19"/>
       <c r="G117" s="19"/>
@@ -6850,17 +7202,20 @@
       <c r="I117" s="19"/>
       <c r="J117" s="19"/>
       <c r="K117" s="19"/>
-      <c r="L117" s="22"/>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="L117" s="19"/>
+      <c r="M117" s="22"/>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A118" s="19" t="s">
         <v>477</v>
       </c>
-      <c r="B118" s="19"/>
-      <c r="C118" s="19" t="s">
+      <c r="B118" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C118" s="19"/>
+      <c r="D118" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="D118" s="19"/>
       <c r="E118" s="19"/>
       <c r="F118" s="19"/>
       <c r="G118" s="19"/>
@@ -6868,17 +7223,20 @@
       <c r="I118" s="19"/>
       <c r="J118" s="19"/>
       <c r="K118" s="19"/>
-      <c r="L118" s="22"/>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="L118" s="19"/>
+      <c r="M118" s="22"/>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A119" s="19" t="s">
         <v>479</v>
       </c>
-      <c r="B119" s="31"/>
-      <c r="C119" s="19" t="s">
+      <c r="B119" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C119" s="30"/>
+      <c r="D119" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="D119" s="19"/>
       <c r="E119" s="19"/>
       <c r="F119" s="19"/>
       <c r="G119" s="19"/>
@@ -6886,19 +7244,22 @@
       <c r="I119" s="19"/>
       <c r="J119" s="19"/>
       <c r="K119" s="19"/>
-      <c r="L119" s="22"/>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="L119" s="19"/>
+      <c r="M119" s="22"/>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A120" s="19" t="s">
         <v>480</v>
       </c>
       <c r="B120" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C120" s="19" t="s">
         <v>481</v>
       </c>
-      <c r="C120" s="19" t="s">
+      <c r="D120" s="19" t="s">
         <v>482</v>
       </c>
-      <c r="D120" s="19"/>
       <c r="E120" s="19"/>
       <c r="F120" s="19"/>
       <c r="G120" s="19"/>
@@ -6906,19 +7267,22 @@
       <c r="I120" s="19"/>
       <c r="J120" s="19"/>
       <c r="K120" s="19"/>
-      <c r="L120" s="22"/>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="L120" s="19"/>
+      <c r="M120" s="22"/>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A121" s="19" t="s">
         <v>483</v>
       </c>
       <c r="B121" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C121" s="19" t="s">
         <v>484</v>
       </c>
-      <c r="C121" s="19" t="s">
+      <c r="D121" s="19" t="s">
         <v>474</v>
       </c>
-      <c r="D121" s="19"/>
       <c r="E121" s="19"/>
       <c r="F121" s="19"/>
       <c r="G121" s="19"/>
@@ -6926,19 +7290,22 @@
       <c r="I121" s="19"/>
       <c r="J121" s="19"/>
       <c r="K121" s="19"/>
-      <c r="L121" s="22"/>
-    </row>
-    <row r="122" spans="1:16" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="L121" s="19"/>
+      <c r="M121" s="22"/>
+    </row>
+    <row r="122" spans="1:17" ht="96" x14ac:dyDescent="0.2">
       <c r="A122" s="19" t="s">
         <v>485</v>
       </c>
       <c r="B122" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C122" s="19" t="s">
         <v>486</v>
       </c>
-      <c r="C122" s="19" t="s">
+      <c r="D122" s="19" t="s">
         <v>487</v>
       </c>
-      <c r="D122" s="19"/>
       <c r="E122" s="19"/>
       <c r="F122" s="19"/>
       <c r="G122" s="19"/>
@@ -6946,25 +7313,28 @@
       <c r="I122" s="19"/>
       <c r="J122" s="19"/>
       <c r="K122" s="19"/>
-      <c r="L122" s="22" t="s">
+      <c r="L122" s="19"/>
+      <c r="M122" s="22" t="s">
         <v>488</v>
       </c>
-      <c r="N122" t="s">
+      <c r="O122" t="s">
         <v>489</v>
       </c>
-      <c r="O122" s="41" t="s">
+      <c r="P122" s="29" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="123" spans="1:16" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:17" ht="96" x14ac:dyDescent="0.2">
       <c r="A123" s="19" t="s">
         <v>491</v>
       </c>
-      <c r="B123" s="31"/>
-      <c r="C123" s="20" t="s">
+      <c r="B123" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C123" s="30"/>
+      <c r="D123" s="20" t="s">
         <v>492</v>
       </c>
-      <c r="D123" s="19"/>
       <c r="E123" s="19"/>
       <c r="F123" s="19"/>
       <c r="G123" s="19"/>
@@ -6972,281 +7342,326 @@
       <c r="I123" s="19"/>
       <c r="J123" s="19"/>
       <c r="K123" s="19"/>
-      <c r="L123" s="22" t="s">
+      <c r="L123" s="19"/>
+      <c r="M123" s="22" t="s">
         <v>493</v>
       </c>
-      <c r="N123" t="s">
+      <c r="O123" t="s">
         <v>494</v>
       </c>
-      <c r="O123" s="41" t="s">
+      <c r="P123" s="29" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="124" spans="1:16" ht="65.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:17" ht="60" x14ac:dyDescent="0.2">
       <c r="A124" s="19" t="s">
         <v>496</v>
       </c>
-      <c r="B124" s="31"/>
-      <c r="C124" s="20" t="s">
+      <c r="B124" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C124" s="30"/>
+      <c r="D124" s="20" t="s">
         <v>497</v>
       </c>
-      <c r="D124" s="19">
+      <c r="E124" s="19">
         <v>1561</v>
       </c>
-      <c r="E124" s="19"/>
       <c r="F124" s="19"/>
       <c r="G124" s="19"/>
-      <c r="H124" s="19">
+      <c r="H124" s="19"/>
+      <c r="I124" s="19">
         <v>1621</v>
       </c>
-      <c r="I124" s="19"/>
       <c r="J124" s="19"/>
       <c r="K124" s="19"/>
-      <c r="L124" s="22"/>
+      <c r="L124" s="19"/>
       <c r="M124" s="22"/>
-      <c r="N124" s="20" t="s">
+      <c r="N124" s="22"/>
+      <c r="O124" s="20" t="s">
         <v>498</v>
       </c>
-      <c r="O124" s="22" t="s">
+      <c r="P124" s="22" t="s">
         <v>499</v>
       </c>
-      <c r="P124" s="19"/>
-    </row>
-    <row r="125" spans="1:16" ht="52.5" x14ac:dyDescent="0.35">
+      <c r="Q124" s="19"/>
+    </row>
+    <row r="125" spans="1:17" ht="60" x14ac:dyDescent="0.2">
       <c r="A125" s="19" t="s">
         <v>500</v>
       </c>
-      <c r="B125" s="32"/>
-      <c r="C125" s="20" t="s">
+      <c r="B125" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C125" s="31"/>
+      <c r="D125" s="20" t="s">
         <v>501</v>
       </c>
-      <c r="N125" s="19" t="s">
+      <c r="O125" s="19" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="126" spans="1:16" ht="174" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:17" ht="176" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>502</v>
       </c>
-      <c r="B126" s="33" t="s">
+      <c r="B126" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C126" t="s">
         <v>503</v>
       </c>
-      <c r="L126" s="30" t="s">
+      <c r="M126" s="29" t="s">
         <v>504</v>
       </c>
-      <c r="O126" s="41" t="s">
+      <c r="P126" s="29" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="127" spans="1:16" ht="116" x14ac:dyDescent="0.35">
-      <c r="A127" s="33" t="s">
+    <row r="127" spans="1:17" ht="128" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
         <v>506</v>
       </c>
-      <c r="B127" s="33" t="s">
+      <c r="B127" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C127" t="s">
         <v>507</v>
       </c>
-      <c r="C127" s="30" t="s">
+      <c r="D127" s="29" t="s">
         <v>508</v>
       </c>
-      <c r="D127">
+      <c r="E127">
         <v>1565</v>
       </c>
-      <c r="H127">
+      <c r="I127">
         <v>1621</v>
       </c>
-      <c r="N127" t="s">
+      <c r="O127" t="s">
         <v>509</v>
       </c>
-      <c r="O127" s="41" t="s">
+      <c r="P127" s="29" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="128" spans="1:16" ht="87" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:17" ht="96" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>511</v>
       </c>
-      <c r="C128" s="30" t="s">
+      <c r="B128" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D128" s="29" t="s">
         <v>512</v>
       </c>
-      <c r="O128" s="41" t="s">
+      <c r="P128" s="29" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="129" spans="1:15" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A129" s="34" t="s">
+    <row r="129" spans="1:16" ht="112" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
         <v>514</v>
       </c>
-      <c r="C129" s="30" t="s">
+      <c r="B129" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D129" s="29" t="s">
         <v>515</v>
       </c>
-      <c r="O129" s="41" t="s">
+      <c r="P129" s="29" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="130" spans="1:15" ht="87" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:16" ht="96" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>517</v>
       </c>
-      <c r="C130" s="30" t="s">
+      <c r="B130" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D130" s="29" t="s">
         <v>518</v>
       </c>
-      <c r="O130" s="41" t="s">
+      <c r="P130" s="29" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="131" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:16" ht="80" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>519</v>
       </c>
-      <c r="C131" s="25" t="s">
+      <c r="B131" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D131" s="25" t="s">
         <v>520</v>
       </c>
-      <c r="D131">
+      <c r="E131">
         <v>1581</v>
       </c>
-      <c r="H131">
+      <c r="I131">
         <v>1617</v>
       </c>
-      <c r="L131" s="30" t="s">
+      <c r="M131" s="29" t="s">
         <v>521</v>
       </c>
-      <c r="N131" t="s">
+      <c r="O131" t="s">
         <v>522</v>
       </c>
-      <c r="O131" s="41" t="s">
+      <c r="P131" s="29" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="132" spans="1:15" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:16" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="19" t="s">
         <v>524</v>
       </c>
       <c r="B132" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C132" s="19" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="19" t="s">
+      <c r="D132" s="19" t="s">
         <v>526</v>
       </c>
-      <c r="D132" s="19"/>
       <c r="E132" s="19"/>
       <c r="F132" s="19"/>
       <c r="G132" s="19"/>
-      <c r="H132" s="19">
+      <c r="H132" s="19"/>
+      <c r="I132" s="19">
         <v>1618</v>
       </c>
-      <c r="I132" s="19"/>
       <c r="J132" s="19"/>
       <c r="K132" s="19"/>
-      <c r="L132" s="22" t="s">
+      <c r="L132" s="19"/>
+      <c r="M132" s="22" t="s">
         <v>527</v>
       </c>
-      <c r="M132" s="22"/>
-      <c r="N132" s="20" t="s">
+      <c r="N132" s="22"/>
+      <c r="O132" s="20" t="s">
         <v>528</v>
       </c>
-      <c r="O132" s="22" t="s">
+      <c r="P132" s="22" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="133" spans="1:15" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:16" ht="240" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>530</v>
       </c>
-      <c r="B133" s="34" t="s">
+      <c r="B133" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C133" t="s">
         <v>531</v>
       </c>
-      <c r="L133" s="30" t="s">
+      <c r="M133" s="29" t="s">
         <v>532</v>
       </c>
-      <c r="O133" s="30" t="s">
+      <c r="P133" s="29" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="134" spans="1:15" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:16" ht="112" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>534</v>
       </c>
-      <c r="B134" s="33" t="s">
+      <c r="B134" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C134" t="s">
         <v>535</v>
       </c>
-      <c r="C134" s="30" t="s">
+      <c r="D134" s="29" t="s">
         <v>536</v>
       </c>
-      <c r="D134">
+      <c r="E134">
         <v>1558</v>
       </c>
-      <c r="H134">
+      <c r="I134">
         <v>1620</v>
       </c>
-      <c r="L134" s="30" t="s">
+      <c r="M134" s="29" t="s">
         <v>537</v>
       </c>
-      <c r="O134" s="30" t="s">
+      <c r="P134" s="29" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="135" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:16" ht="80" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>539</v>
       </c>
-      <c r="B135" s="33" t="s">
+      <c r="B135" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C135" t="s">
         <v>540</v>
       </c>
-      <c r="C135" s="30" t="s">
+      <c r="D135" s="29" t="s">
         <v>541</v>
       </c>
-      <c r="D135">
+      <c r="E135">
         <v>1575</v>
       </c>
-      <c r="H135">
+      <c r="I135">
         <v>1634</v>
       </c>
-      <c r="L135" s="30" t="s">
+      <c r="M135" s="29" t="s">
         <v>542</v>
       </c>
-      <c r="O135" s="30" t="s">
+      <c r="P135" s="29" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="136" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:16" ht="64" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>544</v>
       </c>
-      <c r="B136" s="33" t="s">
+      <c r="B136" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C136" t="s">
         <v>545</v>
       </c>
-      <c r="C136" s="30" t="s">
+      <c r="D136" s="29" t="s">
         <v>546</v>
       </c>
-      <c r="O136" s="41" t="s">
+      <c r="P136" s="29" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="137" spans="1:15" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:16" ht="96" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>548</v>
       </c>
-      <c r="B137" s="30" t="s">
+      <c r="B137" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C137" s="29" t="s">
         <v>549</v>
       </c>
-      <c r="C137" s="30" t="s">
+      <c r="D137" s="29" t="s">
         <v>550</v>
       </c>
-      <c r="L137" s="30" t="s">
+      <c r="M137" s="29" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="138" spans="1:15" ht="53.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:16" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="19" t="s">
         <v>552</v>
       </c>
       <c r="B138" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C138" s="19" t="s">
         <v>553</v>
       </c>
-      <c r="C138" s="19" t="s">
+      <c r="D138" s="19" t="s">
         <v>374</v>
       </c>
-      <c r="D138" s="19"/>
       <c r="E138" s="19"/>
       <c r="F138" s="19"/>
       <c r="G138" s="19"/>
@@ -7254,57 +7669,63 @@
       <c r="I138" s="19"/>
       <c r="J138" s="19"/>
       <c r="K138" s="19"/>
-      <c r="L138" s="22" t="s">
+      <c r="L138" s="19"/>
+      <c r="M138" s="22" t="s">
         <v>554</v>
       </c>
-      <c r="M138" s="22" t="s">
+      <c r="N138" s="22" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="139" spans="1:15" ht="53.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:16" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="19" t="s">
         <v>556</v>
       </c>
-      <c r="B139" s="19"/>
-      <c r="C139" s="19" t="s">
+      <c r="B139" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C139" s="19"/>
+      <c r="D139" s="19" t="s">
         <v>557</v>
       </c>
-      <c r="D139" s="19"/>
       <c r="E139" s="19"/>
       <c r="F139" s="19"/>
-      <c r="G139" s="19" t="s">
+      <c r="G139" s="19"/>
+      <c r="H139" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="H139" s="19">
+      <c r="I139" s="19">
         <v>1645</v>
       </c>
-      <c r="I139" s="19"/>
       <c r="J139" s="19"/>
       <c r="K139" s="19"/>
-      <c r="L139" s="22" t="s">
+      <c r="L139" s="19"/>
+      <c r="M139" s="22" t="s">
         <v>558</v>
       </c>
-      <c r="M139" s="22" t="s">
+      <c r="N139" s="22" t="s">
         <v>559</v>
       </c>
-      <c r="N139" s="20" t="s">
+      <c r="O139" s="20" t="s">
         <v>560</v>
       </c>
-      <c r="O139" s="41" t="s">
+      <c r="P139" s="29" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="140" spans="1:15" ht="208.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:16" ht="180" x14ac:dyDescent="0.2">
       <c r="A140" s="19" t="s">
         <v>562</v>
       </c>
       <c r="B140" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C140" s="19" t="s">
         <v>563</v>
       </c>
-      <c r="C140" s="19" t="s">
+      <c r="D140" s="19" t="s">
         <v>526</v>
       </c>
-      <c r="D140" s="19"/>
       <c r="E140" s="19"/>
       <c r="F140" s="19"/>
       <c r="G140" s="19"/>
@@ -7312,24 +7733,27 @@
       <c r="I140" s="19"/>
       <c r="J140" s="19"/>
       <c r="K140" s="19"/>
-      <c r="L140" s="22" t="s">
+      <c r="L140" s="19"/>
+      <c r="M140" s="22" t="s">
         <v>564</v>
       </c>
-      <c r="M140" s="22" t="s">
+      <c r="N140" s="22" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="141" spans="1:15" ht="208.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:16" ht="225" x14ac:dyDescent="0.2">
       <c r="A141" s="19" t="s">
         <v>566</v>
       </c>
       <c r="B141" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C141" s="19" t="s">
         <v>567</v>
       </c>
-      <c r="C141" s="19" t="s">
+      <c r="D141" s="19" t="s">
         <v>568</v>
       </c>
-      <c r="D141" s="19"/>
       <c r="E141" s="19"/>
       <c r="F141" s="19"/>
       <c r="G141" s="19"/>
@@ -7337,27 +7761,30 @@
       <c r="I141" s="19"/>
       <c r="J141" s="19"/>
       <c r="K141" s="19"/>
-      <c r="L141" s="22" t="s">
+      <c r="L141" s="19"/>
+      <c r="M141" s="22" t="s">
         <v>569</v>
       </c>
-      <c r="N141" s="20" t="s">
+      <c r="O141" s="20" t="s">
         <v>570</v>
       </c>
-      <c r="O141" s="22" t="s">
+      <c r="P141" s="22" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="142" spans="1:15" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:16" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="19" t="s">
         <v>572</v>
       </c>
       <c r="B142" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C142" s="19" t="s">
         <v>567</v>
       </c>
-      <c r="C142" s="19" t="s">
+      <c r="D142" s="19" t="s">
         <v>568</v>
       </c>
-      <c r="D142" s="19"/>
       <c r="E142" s="19"/>
       <c r="F142" s="19"/>
       <c r="G142" s="19"/>
@@ -7365,246 +7792,276 @@
       <c r="I142" s="19"/>
       <c r="J142" s="19"/>
       <c r="K142" s="19"/>
-      <c r="L142" s="22" t="s">
+      <c r="L142" s="19"/>
+      <c r="M142" s="22" t="s">
         <v>573</v>
       </c>
-      <c r="M142" s="22"/>
-      <c r="N142" s="19" t="s">
+      <c r="N142" s="22"/>
+      <c r="O142" s="19" t="s">
         <v>574</v>
       </c>
-      <c r="O142" s="22" t="s">
+      <c r="P142" s="22" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="143" spans="1:15" ht="104.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:16" ht="105" x14ac:dyDescent="0.2">
       <c r="A143" s="19" t="s">
         <v>575</v>
       </c>
       <c r="B143" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C143" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="C143" s="20" t="s">
+      <c r="D143" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="D143" s="19">
+      <c r="E143" s="19">
         <v>1591</v>
       </c>
-      <c r="E143" s="19"/>
       <c r="F143" s="19"/>
       <c r="G143" s="19"/>
-      <c r="H143" s="19">
+      <c r="H143" s="19"/>
+      <c r="I143" s="19">
         <v>1656</v>
       </c>
-      <c r="M143" s="22" t="s">
+      <c r="N143" s="22" t="s">
         <v>578</v>
       </c>
-      <c r="N143" s="19" t="s">
+      <c r="O143" s="19" t="s">
         <v>579</v>
       </c>
-      <c r="O143" s="22" t="s">
+      <c r="P143" s="22" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="144" spans="1:15" ht="78.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:16" ht="90" x14ac:dyDescent="0.2">
       <c r="A144" s="20" t="s">
         <v>581</v>
       </c>
-      <c r="B144" s="20"/>
-      <c r="C144" s="20" t="s">
+      <c r="B144" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C144" s="20"/>
+      <c r="D144" s="20" t="s">
         <v>582</v>
       </c>
-      <c r="D144" s="19">
+      <c r="E144" s="19">
         <v>1563</v>
       </c>
-      <c r="E144" s="19"/>
       <c r="F144" s="19"/>
       <c r="G144" s="19"/>
-      <c r="H144" s="19">
+      <c r="H144" s="19"/>
+      <c r="I144" s="19">
         <v>1617</v>
       </c>
-      <c r="I144" s="19"/>
-      <c r="M144" s="22" t="s">
+      <c r="J144" s="19"/>
+      <c r="N144" s="22" t="s">
         <v>583</v>
       </c>
-      <c r="N144" s="20"/>
-      <c r="O144" s="22" t="s">
+      <c r="O144" s="20"/>
+      <c r="P144" s="22" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="145" spans="1:15" ht="78.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:16" ht="90" x14ac:dyDescent="0.2">
       <c r="A145" s="20" t="s">
         <v>585</v>
       </c>
-      <c r="B145" s="20"/>
-      <c r="C145" s="20" t="s">
+      <c r="B145" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C145" s="20"/>
+      <c r="D145" s="20" t="s">
         <v>586</v>
       </c>
-      <c r="D145" s="19">
+      <c r="E145" s="19">
         <v>1588</v>
       </c>
-      <c r="E145" s="19"/>
       <c r="F145" s="19"/>
       <c r="G145" s="19"/>
-      <c r="H145" s="19">
+      <c r="H145" s="19"/>
+      <c r="I145" s="19">
         <v>1635</v>
       </c>
-      <c r="I145" s="19"/>
-      <c r="M145" s="22" t="s">
+      <c r="J145" s="19"/>
+      <c r="N145" s="22" t="s">
         <v>587</v>
       </c>
-      <c r="N145" s="20" t="s">
+      <c r="O145" s="20" t="s">
         <v>588</v>
       </c>
-      <c r="O145" s="22" t="s">
+      <c r="P145" s="22" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="146" spans="1:15" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:16" ht="120" x14ac:dyDescent="0.2">
       <c r="A146" s="20" t="s">
         <v>590</v>
       </c>
       <c r="B146" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C146" s="20" t="s">
         <v>591</v>
       </c>
-      <c r="C146" s="20" t="s">
+      <c r="D146" s="20" t="s">
         <v>586</v>
       </c>
-      <c r="D146" s="19">
+      <c r="E146" s="19">
         <v>1586</v>
       </c>
-      <c r="E146" s="19"/>
       <c r="F146" s="19"/>
       <c r="G146" s="19"/>
-      <c r="H146" s="19">
+      <c r="H146" s="19"/>
+      <c r="I146" s="19">
         <v>1618</v>
       </c>
-      <c r="I146" s="19"/>
-      <c r="M146" s="22" t="s">
+      <c r="J146" s="19"/>
+      <c r="N146" s="22" t="s">
         <v>592</v>
       </c>
-      <c r="N146" s="20"/>
-      <c r="O146" s="22"/>
-    </row>
-    <row r="147" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O146" s="20"/>
+      <c r="P146" s="22"/>
+    </row>
+    <row r="147" spans="1:16" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="20" t="s">
         <v>593</v>
       </c>
       <c r="B147" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C147" s="20" t="s">
         <v>591</v>
       </c>
-      <c r="C147" s="20" t="s">
+      <c r="D147" s="20" t="s">
         <v>586</v>
       </c>
-      <c r="D147" s="19">
+      <c r="E147" s="19">
         <v>1587</v>
       </c>
-      <c r="E147" s="19"/>
       <c r="F147" s="19"/>
       <c r="G147" s="19"/>
-      <c r="H147" s="19">
+      <c r="H147" s="19"/>
+      <c r="I147" s="19">
         <v>1627</v>
       </c>
-      <c r="I147" s="19"/>
-      <c r="M147" s="22"/>
-      <c r="N147" s="20" t="s">
+      <c r="J147" s="19"/>
+      <c r="N147" s="22"/>
+      <c r="O147" s="20" t="s">
         <v>588</v>
       </c>
-      <c r="O147" s="22" t="s">
+      <c r="P147" s="22" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="148" spans="1:15" ht="83.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:16" ht="83.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="20" t="s">
         <v>595</v>
       </c>
       <c r="B148" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C148" s="20" t="s">
         <v>596</v>
       </c>
-      <c r="C148" s="20" t="s">
+      <c r="D148" s="20" t="s">
         <v>597</v>
       </c>
-      <c r="D148" s="19">
+      <c r="E148" s="19">
         <v>1554</v>
       </c>
-      <c r="E148" s="19"/>
       <c r="F148" s="19"/>
       <c r="G148" s="19"/>
-      <c r="H148" s="19">
+      <c r="H148" s="19"/>
+      <c r="I148" s="19">
         <v>1613</v>
       </c>
-      <c r="M148" s="22" t="s">
+      <c r="N148" s="22" t="s">
         <v>598</v>
       </c>
-      <c r="O148" s="41" t="s">
+      <c r="P148" s="29" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="149" spans="1:15" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="20" t="s">
         <v>600</v>
       </c>
       <c r="B149" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C149" s="20" t="s">
         <v>596</v>
       </c>
-      <c r="C149" s="20" t="s">
+      <c r="D149" s="20" t="s">
         <v>601</v>
       </c>
-      <c r="D149" s="19">
+      <c r="E149" s="19">
         <v>1587</v>
       </c>
-      <c r="E149" s="19"/>
       <c r="F149" s="19"/>
       <c r="G149" s="19"/>
-      <c r="H149" s="19">
+      <c r="H149" s="19"/>
+      <c r="I149" s="19">
         <v>1627</v>
       </c>
     </row>
-    <row r="150" spans="1:15" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:16" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="19" t="s">
         <v>602</v>
       </c>
       <c r="B150" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C150" s="19" t="s">
         <v>603</v>
       </c>
-      <c r="C150" s="19" t="s">
+      <c r="D150" s="19" t="s">
         <v>604</v>
       </c>
-      <c r="M150" s="22" t="s">
+      <c r="N150" s="22" t="s">
         <v>605</v>
       </c>
-      <c r="N150" s="20" t="s">
+      <c r="O150" s="20" t="s">
         <v>606</v>
       </c>
-      <c r="O150" s="41" t="s">
+      <c r="P150" s="29" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="151" spans="1:15" ht="104.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:16" ht="105" x14ac:dyDescent="0.2">
       <c r="A151" s="19" t="s">
         <v>608</v>
       </c>
       <c r="B151" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C151" s="19" t="s">
         <v>609</v>
       </c>
-      <c r="C151" s="19" t="s">
+      <c r="D151" s="19" t="s">
         <v>610</v>
       </c>
-      <c r="L151" s="22" t="s">
+      <c r="M151" s="22" t="s">
         <v>611</v>
       </c>
-      <c r="M151" s="22" t="s">
+      <c r="N151" s="22" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="152" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:16" ht="45" x14ac:dyDescent="0.2">
       <c r="A152" s="19" t="s">
         <v>613</v>
       </c>
-      <c r="B152" s="19"/>
-      <c r="C152" s="19" t="s">
+      <c r="B152" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C152" s="19"/>
+      <c r="D152" s="19" t="s">
         <v>614</v>
       </c>
-      <c r="D152" s="19"/>
       <c r="E152" s="19"/>
       <c r="F152" s="19"/>
       <c r="G152" s="19"/>
@@ -7612,25 +8069,28 @@
       <c r="I152" s="19"/>
       <c r="J152" s="19"/>
       <c r="K152" s="19"/>
-      <c r="L152" s="22"/>
-      <c r="M152" s="22" t="s">
+      <c r="L152" s="19"/>
+      <c r="M152" s="22"/>
+      <c r="N152" s="22" t="s">
         <v>615</v>
       </c>
-      <c r="N152" s="19" t="s">
+      <c r="O152" s="19" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="153" spans="1:15" ht="78.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:16" ht="75" x14ac:dyDescent="0.2">
       <c r="A153" s="19" t="s">
         <v>617</v>
       </c>
       <c r="B153" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C153" s="19" t="s">
         <v>618</v>
       </c>
-      <c r="C153" s="19" t="s">
+      <c r="D153" s="19" t="s">
         <v>374</v>
       </c>
-      <c r="D153" s="19"/>
       <c r="E153" s="19"/>
       <c r="F153" s="19"/>
       <c r="G153" s="19"/>
@@ -7638,25 +8098,28 @@
       <c r="I153" s="19"/>
       <c r="J153" s="19"/>
       <c r="K153" s="19"/>
-      <c r="L153" s="22" t="s">
+      <c r="L153" s="19"/>
+      <c r="M153" s="22" t="s">
         <v>619</v>
       </c>
-      <c r="M153" s="22" t="s">
+      <c r="N153" s="22" t="s">
         <v>620</v>
       </c>
-      <c r="N153" s="19" t="s">
+      <c r="O153" s="19" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="154" spans="1:15" ht="143.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:16" ht="150" x14ac:dyDescent="0.2">
       <c r="A154" s="19" t="s">
         <v>622</v>
       </c>
-      <c r="B154" s="19"/>
-      <c r="C154" s="19" t="s">
+      <c r="B154" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C154" s="19"/>
+      <c r="D154" s="19" t="s">
         <v>374</v>
       </c>
-      <c r="D154" s="19"/>
       <c r="E154" s="19"/>
       <c r="F154" s="19"/>
       <c r="G154" s="19"/>
@@ -7664,1616 +8127,1893 @@
       <c r="I154" s="19"/>
       <c r="J154" s="19"/>
       <c r="K154" s="19"/>
-      <c r="L154" s="22" t="s">
+      <c r="L154" s="19"/>
+      <c r="M154" s="22" t="s">
         <v>623</v>
       </c>
-      <c r="M154" s="22" t="s">
+      <c r="N154" s="22" t="s">
         <v>624</v>
       </c>
-      <c r="N154" s="19" t="s">
+      <c r="O154" s="19" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="155" spans="1:15" ht="65.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:16" ht="60" x14ac:dyDescent="0.2">
       <c r="A155" s="19" t="s">
         <v>626</v>
       </c>
-      <c r="B155" s="19"/>
-      <c r="C155" s="19" t="s">
+      <c r="B155" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C155" s="19"/>
+      <c r="D155" s="19" t="s">
         <v>627</v>
       </c>
-      <c r="M155" s="22" t="s">
+      <c r="N155" s="22" t="s">
         <v>628</v>
       </c>
-      <c r="N155" s="19" t="s">
+      <c r="O155" s="19" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="156" spans="1:15" ht="104.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:16" ht="105" x14ac:dyDescent="0.2">
       <c r="A156" s="19" t="s">
         <v>630</v>
       </c>
       <c r="B156" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C156" s="19" t="s">
         <v>631</v>
       </c>
-      <c r="C156" s="19" t="s">
+      <c r="D156" s="19" t="s">
         <v>632</v>
       </c>
-      <c r="G156" s="19" t="s">
+      <c r="H156" s="19" t="s">
         <v>633</v>
       </c>
-      <c r="M156" s="22" t="s">
+      <c r="N156" s="22" t="s">
         <v>634</v>
       </c>
-      <c r="N156" s="20" t="s">
+      <c r="O156" s="20" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="157" spans="1:15" ht="156.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:16" ht="150" x14ac:dyDescent="0.2">
       <c r="A157" s="20" t="s">
         <v>636</v>
       </c>
-      <c r="B157" s="19"/>
-      <c r="C157" s="20" t="s">
+      <c r="B157" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C157" s="19"/>
+      <c r="D157" s="20" t="s">
         <v>637</v>
       </c>
-      <c r="G157" s="19" t="s">
+      <c r="H157" s="19" t="s">
         <v>638</v>
       </c>
-      <c r="H157" s="19">
+      <c r="I157" s="19">
         <v>1620</v>
       </c>
-      <c r="K157" s="19"/>
-      <c r="L157" s="22"/>
-      <c r="M157" s="22" t="s">
+      <c r="L157" s="19"/>
+      <c r="M157" s="22"/>
+      <c r="N157" s="22" t="s">
         <v>639</v>
       </c>
-      <c r="N157" s="20" t="s">
+      <c r="O157" s="20" t="s">
         <v>640</v>
       </c>
-      <c r="O157" s="22"/>
-    </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P157" s="22"/>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A158" s="19" t="s">
         <v>641</v>
       </c>
-      <c r="B158" s="19"/>
-      <c r="C158" s="19" t="s">
+      <c r="B158" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C158" s="19"/>
+      <c r="D158" s="19" t="s">
         <v>642</v>
       </c>
-      <c r="D158" s="19">
+      <c r="E158" s="19">
         <v>1533</v>
       </c>
-      <c r="E158" s="19"/>
       <c r="F158" s="19"/>
       <c r="G158" s="19"/>
-      <c r="H158" s="19">
+      <c r="H158" s="19"/>
+      <c r="I158" s="19">
         <v>1584</v>
       </c>
-      <c r="K158" s="19"/>
-      <c r="L158" s="22"/>
+      <c r="L158" s="19"/>
       <c r="M158" s="22"/>
-      <c r="N158" s="19"/>
-      <c r="O158" s="22"/>
-    </row>
-    <row r="159" spans="1:15" ht="78.5" x14ac:dyDescent="0.35">
+      <c r="N158" s="22"/>
+      <c r="O158" s="19"/>
+      <c r="P158" s="22"/>
+    </row>
+    <row r="159" spans="1:16" ht="75" x14ac:dyDescent="0.2">
       <c r="A159" s="19" t="s">
         <v>643</v>
       </c>
       <c r="B159" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C159" s="19" t="s">
         <v>644</v>
       </c>
-      <c r="C159" s="20" t="s">
+      <c r="D159" s="20" t="s">
         <v>645</v>
       </c>
-      <c r="D159" s="19">
+      <c r="E159" s="19">
         <v>1562</v>
       </c>
-      <c r="E159" s="19"/>
       <c r="F159" s="19"/>
       <c r="G159" s="19"/>
-      <c r="H159" s="19">
+      <c r="H159" s="19"/>
+      <c r="I159" s="19">
         <v>1625</v>
       </c>
-      <c r="K159" s="19"/>
-      <c r="L159" s="22" t="s">
+      <c r="L159" s="19"/>
+      <c r="M159" s="22" t="s">
         <v>646</v>
       </c>
-      <c r="N159" s="19"/>
-      <c r="O159" s="22" t="s">
+      <c r="O159" s="19"/>
+      <c r="P159" s="22" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="160" spans="1:15" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:16" ht="45" x14ac:dyDescent="0.2">
       <c r="A160" s="19" t="s">
         <v>648</v>
       </c>
       <c r="B160" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C160" s="19" t="s">
         <v>649</v>
       </c>
-      <c r="C160" s="20" t="s">
+      <c r="D160" s="20" t="s">
         <v>650</v>
       </c>
-      <c r="N160" s="19" t="s">
+      <c r="O160" s="19" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="161" spans="1:15" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:16" ht="45" x14ac:dyDescent="0.2">
       <c r="A161" s="19" t="s">
         <v>652</v>
       </c>
       <c r="B161" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C161" s="19" t="s">
         <v>653</v>
       </c>
-      <c r="C161" s="20" t="s">
+      <c r="D161" s="20" t="s">
         <v>654</v>
       </c>
-      <c r="D161" s="19">
+      <c r="E161" s="19">
         <v>1577</v>
       </c>
-      <c r="E161" s="19"/>
       <c r="F161" s="19"/>
       <c r="G161" s="19"/>
-      <c r="H161" s="19">
+      <c r="H161" s="19"/>
+      <c r="I161" s="19">
         <v>1633</v>
       </c>
-      <c r="L161" s="22" t="s">
+      <c r="M161" s="22" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="162" spans="1:15" ht="104.5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:16" ht="90" x14ac:dyDescent="0.2">
       <c r="A162" s="19" t="s">
         <v>656</v>
       </c>
       <c r="B162" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C162" s="19" t="s">
         <v>657</v>
       </c>
-      <c r="C162" s="19" t="s">
+      <c r="D162" s="19" t="s">
         <v>658</v>
       </c>
-      <c r="D162" s="19">
+      <c r="E162" s="19">
         <v>1563</v>
       </c>
-      <c r="E162" s="19"/>
       <c r="F162" s="19"/>
       <c r="G162" s="19"/>
-      <c r="H162" s="19">
+      <c r="H162" s="19"/>
+      <c r="I162" s="19">
         <v>1641</v>
       </c>
-      <c r="L162" s="22" t="s">
+      <c r="M162" s="22" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="163" spans="1:15" ht="104.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:16" ht="90" x14ac:dyDescent="0.2">
       <c r="A163" s="19" t="s">
         <v>660</v>
       </c>
       <c r="B163" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C163" s="19" t="s">
         <v>661</v>
       </c>
-      <c r="C163" s="19" t="s">
+      <c r="D163" s="19" t="s">
         <v>662</v>
       </c>
-      <c r="D163" s="19">
+      <c r="E163" s="19">
         <v>1560</v>
       </c>
-      <c r="E163" s="19"/>
       <c r="F163" s="19"/>
       <c r="G163" s="19"/>
-      <c r="H163" s="19">
+      <c r="H163" s="19"/>
+      <c r="I163" s="19">
         <v>1609</v>
       </c>
-      <c r="L163" s="22" t="s">
+      <c r="M163" s="22" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="164" spans="1:15" ht="91.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:16" ht="90" x14ac:dyDescent="0.2">
       <c r="A164" s="19" t="s">
         <v>664</v>
       </c>
       <c r="B164" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C164" s="19" t="s">
         <v>665</v>
       </c>
-      <c r="C164" s="19" t="s">
+      <c r="D164" s="19" t="s">
         <v>666</v>
       </c>
-      <c r="D164" s="19">
+      <c r="E164" s="19">
         <v>1581</v>
       </c>
-      <c r="E164" s="19"/>
       <c r="F164" s="19"/>
       <c r="G164" s="19"/>
-      <c r="H164" s="19">
+      <c r="H164" s="19"/>
+      <c r="I164" s="19">
         <v>1641</v>
       </c>
-      <c r="L164" s="22" t="s">
+      <c r="M164" s="22" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="165" spans="1:15" ht="104.5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:16" ht="105" x14ac:dyDescent="0.2">
       <c r="A165" s="19" t="s">
         <v>668</v>
       </c>
       <c r="B165" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C165" s="19" t="s">
         <v>669</v>
       </c>
-      <c r="C165" s="19" t="s">
+      <c r="D165" s="19" t="s">
         <v>670</v>
       </c>
-      <c r="D165" s="19">
+      <c r="E165" s="19">
         <v>1558</v>
       </c>
-      <c r="E165" s="19"/>
       <c r="F165" s="19"/>
       <c r="G165" s="19"/>
-      <c r="H165" s="19">
+      <c r="H165" s="19"/>
+      <c r="I165" s="19">
         <v>1645</v>
       </c>
-      <c r="L165" s="22" t="s">
+      <c r="M165" s="22" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="166" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>672</v>
       </c>
-      <c r="C166" s="25" t="s">
+      <c r="B166" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D166" s="25" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="167" spans="1:15" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:16" ht="45" x14ac:dyDescent="0.2">
       <c r="A167" s="19" t="s">
         <v>674</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B167" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C167" t="s">
         <v>675</v>
       </c>
-      <c r="C167" t="s">
+      <c r="D167" t="s">
         <v>676</v>
       </c>
-      <c r="D167" s="19">
+      <c r="E167" s="19">
         <v>1566</v>
       </c>
-      <c r="E167" s="19"/>
       <c r="F167" s="19"/>
       <c r="G167" s="19"/>
-      <c r="H167" s="19">
+      <c r="H167" s="19"/>
+      <c r="I167" s="19">
         <v>1633</v>
       </c>
-      <c r="L167" s="22" t="s">
+      <c r="M167" s="22" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="168" spans="1:15" ht="58" x14ac:dyDescent="0.35">
-      <c r="A168" s="33" t="s">
+    <row r="168" spans="1:16" ht="64" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
         <v>678</v>
       </c>
-      <c r="C168" s="25" t="s">
+      <c r="B168" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D168" s="25" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="169" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:16" ht="64" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>680</v>
       </c>
-      <c r="C169" s="25" t="s">
+      <c r="B169" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D169" s="25" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="170" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:16" ht="64" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>681</v>
       </c>
-      <c r="L170" s="30" t="s">
+      <c r="B170" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M170" s="29" t="s">
         <v>682</v>
       </c>
-      <c r="M170" s="30" t="s">
+      <c r="N170" s="29" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>684</v>
       </c>
-      <c r="C171" t="s">
+      <c r="B171" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D171" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>686</v>
       </c>
-      <c r="C172" s="33" t="s">
+      <c r="B172" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D172" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="173" spans="1:15" ht="87" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:16" ht="96" x14ac:dyDescent="0.2">
       <c r="A173" s="25" t="s">
         <v>688</v>
       </c>
-      <c r="C173" s="25" t="s">
+      <c r="B173" s="25" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D173" s="25" t="s">
         <v>689</v>
       </c>
-      <c r="L173" s="41" t="s">
+      <c r="M173" s="29" t="s">
         <v>690</v>
       </c>
-      <c r="N173" t="s">
+      <c r="O173" t="s">
         <v>691</v>
       </c>
-      <c r="O173" s="30" t="s">
+      <c r="P173" s="29" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="174" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A174" s="19" t="s">
         <v>693</v>
       </c>
-      <c r="B174" s="19"/>
-      <c r="C174" s="19" t="s">
+      <c r="B174" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C174" s="19"/>
+      <c r="D174" s="19" t="s">
         <v>694</v>
       </c>
-      <c r="D174" s="19">
+      <c r="E174" s="19">
         <v>1563</v>
       </c>
-      <c r="E174" s="19"/>
       <c r="F174" s="19"/>
       <c r="G174" s="19"/>
-      <c r="H174" s="19">
+      <c r="H174" s="19"/>
+      <c r="I174" s="19">
         <v>1624</v>
       </c>
-      <c r="L174" s="22" t="s">
+      <c r="M174" s="22" t="s">
         <v>695</v>
       </c>
-      <c r="M174" s="22"/>
-    </row>
-    <row r="175" spans="1:15" ht="39.5" x14ac:dyDescent="0.35">
+      <c r="N174" s="22"/>
+    </row>
+    <row r="175" spans="1:16" ht="45" x14ac:dyDescent="0.2">
       <c r="A175" s="19" t="s">
         <v>696</v>
       </c>
-      <c r="B175" s="19"/>
+      <c r="B175" s="19" t="s">
+        <v>1035</v>
+      </c>
       <c r="C175" s="19"/>
-      <c r="D175" s="19">
+      <c r="D175" s="19"/>
+      <c r="E175" s="19">
         <v>1593</v>
       </c>
-      <c r="E175" s="19"/>
       <c r="F175" s="19"/>
       <c r="G175" s="19"/>
-      <c r="H175" s="19">
+      <c r="H175" s="19"/>
+      <c r="I175" s="19">
         <v>1663</v>
       </c>
-      <c r="L175" s="22" t="s">
+      <c r="M175" s="22" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="176" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:16" ht="80" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>698</v>
       </c>
-      <c r="C176" t="s">
+      <c r="B176" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D176" t="s">
         <v>699</v>
       </c>
-      <c r="L176" s="30" t="s">
+      <c r="M176" s="29" t="s">
         <v>700</v>
       </c>
-      <c r="O176" s="41" t="s">
+      <c r="P176" s="29" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>702</v>
       </c>
-      <c r="C177" t="s">
+      <c r="B177" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D177" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>703</v>
       </c>
-      <c r="C178" t="s">
+      <c r="B178" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D178" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="179" spans="1:15" ht="78.5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:16" ht="75" x14ac:dyDescent="0.2">
       <c r="A179" s="19" t="s">
         <v>704</v>
       </c>
       <c r="B179" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C179" s="19" t="s">
         <v>705</v>
       </c>
-      <c r="C179" s="19" t="s">
+      <c r="D179" s="19" t="s">
         <v>706</v>
       </c>
-      <c r="H179">
+      <c r="I179">
         <v>1619</v>
       </c>
-      <c r="L179" s="22" t="s">
+      <c r="M179" s="22" t="s">
         <v>707</v>
       </c>
-      <c r="N179" s="19" t="s">
+      <c r="O179" s="19" t="s">
         <v>708</v>
       </c>
-      <c r="O179" s="30" t="s">
+      <c r="P179" s="29" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="180" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>710</v>
       </c>
-      <c r="C180" s="25" t="s">
+      <c r="B180" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D180" s="25" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="181" spans="1:15" ht="145" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:16" ht="160" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>712</v>
       </c>
       <c r="B181" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C181" t="s">
         <v>713</v>
       </c>
-      <c r="C181" s="25" t="s">
+      <c r="D181" s="25" t="s">
         <v>714</v>
       </c>
-      <c r="H181">
+      <c r="I181">
         <v>1627</v>
       </c>
-      <c r="L181" s="30" t="s">
+      <c r="M181" s="29" t="s">
         <v>715</v>
       </c>
-      <c r="O181" s="41" t="s">
+      <c r="P181" s="29" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="182" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:16" ht="64" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>717</v>
       </c>
-      <c r="C182" s="25" t="s">
+      <c r="B182" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D182" s="25" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="183" spans="1:15" ht="406" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A183" s="19" t="s">
         <v>719</v>
       </c>
-      <c r="B183" s="19"/>
-      <c r="C183" s="19" t="s">
+      <c r="B183" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C183" s="19"/>
+      <c r="D183" s="19" t="s">
         <v>720</v>
       </c>
-      <c r="H183" s="19">
+      <c r="I183" s="19">
         <v>1629</v>
       </c>
-      <c r="K183" s="19"/>
-      <c r="O183" s="41" t="s">
+      <c r="L183" s="19"/>
+      <c r="P183" s="29" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="184" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A184" s="19" t="s">
         <v>722</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B184" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C184" t="s">
         <v>723</v>
       </c>
-      <c r="C184" s="25" t="s">
+      <c r="D184" s="25" t="s">
         <v>724</v>
       </c>
-      <c r="M184" s="22" t="s">
+      <c r="N184" s="22" t="s">
         <v>725</v>
       </c>
-      <c r="N184" s="19" t="s">
+      <c r="O184" s="19" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="185" spans="1:15" ht="391.5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A185" s="19" t="s">
         <v>726</v>
       </c>
       <c r="B185" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C185" s="19" t="s">
         <v>727</v>
       </c>
-      <c r="C185" s="19" t="s">
+      <c r="D185" s="19" t="s">
         <v>720</v>
       </c>
-      <c r="L185" s="22" t="s">
+      <c r="M185" s="22" t="s">
         <v>728</v>
       </c>
-      <c r="O185" s="41" t="s">
+      <c r="P185" s="29" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="186" spans="1:15" ht="391.5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A186" s="19" t="s">
         <v>730</v>
       </c>
       <c r="B186" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C186" s="19" t="s">
         <v>727</v>
       </c>
-      <c r="C186" s="19" t="s">
+      <c r="D186" s="19" t="s">
         <v>720</v>
       </c>
-      <c r="L186" s="22" t="s">
+      <c r="M186" s="22" t="s">
         <v>731</v>
       </c>
-      <c r="O186" s="41" t="s">
+      <c r="P186" s="29" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="187" spans="1:15" ht="391.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:16" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A187" s="19" t="s">
         <v>732</v>
       </c>
-      <c r="B187" s="19"/>
-      <c r="C187" s="19" t="s">
+      <c r="B187" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C187" s="19"/>
+      <c r="D187" s="19" t="s">
         <v>720</v>
       </c>
-      <c r="L187" s="22" t="s">
+      <c r="M187" s="22" t="s">
         <v>733</v>
       </c>
-      <c r="M187" s="22" t="s">
+      <c r="N187" s="22" t="s">
         <v>734</v>
       </c>
-      <c r="O187" s="41" t="s">
+      <c r="P187" s="29" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A188" s="19" t="s">
         <v>735</v>
       </c>
       <c r="B188" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C188" s="19" t="s">
         <v>736</v>
       </c>
-      <c r="C188" s="19" t="s">
+      <c r="D188" s="19" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A189" s="19" t="s">
         <v>738</v>
       </c>
       <c r="B189" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C189" s="19" t="s">
         <v>739</v>
       </c>
-      <c r="C189" s="19" t="s">
+      <c r="D189" s="19" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A190" s="19" t="s">
         <v>741</v>
       </c>
       <c r="B190" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C190" s="19" t="s">
         <v>742</v>
       </c>
-      <c r="C190" s="19" t="s">
+      <c r="D190" s="19" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A191" s="19" t="s">
         <v>744</v>
       </c>
       <c r="B191" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C191" s="19" t="s">
         <v>745</v>
       </c>
-      <c r="C191" s="19" t="s">
+      <c r="D191" s="19" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A192" s="19" t="s">
         <v>747</v>
       </c>
-      <c r="B192" s="19"/>
-      <c r="C192" s="19" t="s">
+      <c r="B192" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C192" s="19"/>
+      <c r="D192" s="19" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A193" s="19" t="s">
         <v>749</v>
       </c>
-      <c r="B193" s="19"/>
-      <c r="C193" s="19" t="s">
+      <c r="B193" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C193" s="19"/>
+      <c r="D193" s="19" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A194" s="19" t="s">
         <v>751</v>
       </c>
-      <c r="B194" s="19"/>
-      <c r="C194" s="19" t="s">
+      <c r="B194" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C194" s="19"/>
+      <c r="D194" s="19" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A195" s="19" t="s">
         <v>753</v>
       </c>
       <c r="B195" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C195" s="19" t="s">
         <v>754</v>
       </c>
-      <c r="C195" s="19" t="s">
+      <c r="D195" s="19" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A196" s="19" t="s">
         <v>756</v>
       </c>
       <c r="B196" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C196" s="19" t="s">
         <v>757</v>
       </c>
-      <c r="C196" s="19" t="s">
+      <c r="D196" s="19" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A197" s="19" t="s">
         <v>759</v>
       </c>
-      <c r="B197" s="35"/>
-      <c r="C197" s="19" t="s">
+      <c r="B197" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C197" s="19"/>
+      <c r="D197" s="19" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A198" s="19" t="s">
         <v>761</v>
       </c>
       <c r="B198" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C198" s="19" t="s">
         <v>762</v>
       </c>
-      <c r="C198" s="19" t="s">
+      <c r="D198" s="19" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="199" spans="1:14" ht="78.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:15" ht="75" x14ac:dyDescent="0.2">
       <c r="A199" s="19" t="s">
         <v>764</v>
       </c>
-      <c r="B199" s="19"/>
-      <c r="C199" s="19" t="s">
+      <c r="B199" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C199" s="19"/>
+      <c r="D199" s="19" t="s">
         <v>765</v>
       </c>
-      <c r="D199" s="19">
+      <c r="E199" s="19">
         <v>1573</v>
       </c>
-      <c r="E199" s="19"/>
       <c r="F199" s="19"/>
       <c r="G199" s="19"/>
-      <c r="H199" s="19">
+      <c r="H199" s="19"/>
+      <c r="I199" s="19">
         <v>1651</v>
       </c>
-      <c r="L199" s="22" t="s">
+      <c r="M199" s="22" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="200" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A200" s="20" t="s">
         <v>767</v>
       </c>
-      <c r="B200" s="19"/>
-      <c r="C200" s="19" t="s">
+      <c r="B200" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C200" s="19"/>
+      <c r="D200" s="19" t="s">
         <v>768</v>
       </c>
-      <c r="D200" s="19">
+      <c r="E200" s="19">
         <v>1578</v>
       </c>
-      <c r="E200" s="19"/>
       <c r="F200" s="19"/>
       <c r="G200" s="19"/>
-      <c r="H200" s="19">
+      <c r="H200" s="19"/>
+      <c r="I200" s="19">
         <v>1624</v>
       </c>
-      <c r="L200" s="22" t="s">
+      <c r="M200" s="22" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="201" spans="1:14" ht="117.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:15" ht="120" x14ac:dyDescent="0.2">
       <c r="A201" s="19" t="s">
         <v>770</v>
       </c>
-      <c r="B201" s="19"/>
-      <c r="C201" s="19" t="s">
+      <c r="B201" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C201" s="19"/>
+      <c r="D201" s="19" t="s">
         <v>771</v>
       </c>
-      <c r="D201" s="19">
+      <c r="E201" s="19">
         <v>1588</v>
       </c>
-      <c r="E201" s="19"/>
       <c r="F201" s="19"/>
       <c r="G201" s="19"/>
-      <c r="H201" s="19">
+      <c r="H201" s="19"/>
+      <c r="I201" s="19">
         <v>1650</v>
       </c>
-      <c r="L201" s="22" t="s">
+      <c r="M201" s="22" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="202" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A202" s="19" t="s">
         <v>773</v>
       </c>
-      <c r="B202" s="19"/>
-      <c r="C202" s="20" t="s">
+      <c r="B202" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C202" s="19"/>
+      <c r="D202" s="20" t="s">
         <v>774</v>
       </c>
-      <c r="N202" t="s">
+      <c r="O202" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="203" spans="1:14" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A203" s="19" t="s">
         <v>776</v>
       </c>
-      <c r="B203" s="19"/>
-      <c r="C203" s="20" t="s">
+      <c r="B203" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C203" s="19"/>
+      <c r="D203" s="20" t="s">
         <v>777</v>
       </c>
-      <c r="H203">
+      <c r="I203">
         <v>1625</v>
       </c>
-      <c r="L203" s="41" t="s">
+      <c r="M203" s="29" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="204" spans="1:14" ht="65.5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:15" ht="60" x14ac:dyDescent="0.2">
       <c r="A204" s="19" t="s">
         <v>779</v>
       </c>
-      <c r="B204" s="19"/>
-      <c r="C204" s="19" t="s">
+      <c r="B204" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C204" s="19"/>
+      <c r="D204" s="19" t="s">
         <v>780</v>
       </c>
-      <c r="D204" s="19">
+      <c r="E204" s="19">
         <v>1609</v>
       </c>
-      <c r="E204" s="19"/>
       <c r="F204" s="19"/>
       <c r="G204" s="19"/>
-      <c r="H204" s="19">
+      <c r="H204" s="19"/>
+      <c r="I204" s="19">
         <v>1670</v>
       </c>
-      <c r="L204" s="22" t="s">
+      <c r="M204" s="22" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="205" spans="1:14" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:15" ht="45" x14ac:dyDescent="0.2">
       <c r="A205" s="19" t="s">
         <v>782</v>
       </c>
       <c r="B205" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C205" s="19" t="s">
         <v>783</v>
       </c>
-      <c r="C205" s="19" t="s">
+      <c r="D205" s="19" t="s">
         <v>784</v>
       </c>
-      <c r="D205" s="19">
+      <c r="E205" s="19">
         <v>1579</v>
       </c>
-      <c r="E205" s="19"/>
       <c r="F205" s="19"/>
       <c r="G205" s="19"/>
-      <c r="H205" s="19">
+      <c r="H205" s="19"/>
+      <c r="I205" s="19">
         <v>1634</v>
       </c>
-      <c r="L205" s="22" t="s">
+      <c r="M205" s="22" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="206" spans="1:14" ht="117.5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:15" ht="120" x14ac:dyDescent="0.2">
       <c r="A206" s="19" t="s">
         <v>786</v>
       </c>
-      <c r="B206" s="19"/>
-      <c r="C206" s="19" t="s">
+      <c r="B206" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C206" s="19"/>
+      <c r="D206" s="19" t="s">
         <v>787</v>
       </c>
-      <c r="D206" s="19">
+      <c r="E206" s="19">
         <v>1550</v>
       </c>
-      <c r="E206" s="19"/>
       <c r="F206" s="19"/>
       <c r="G206" s="19"/>
-      <c r="H206" s="19">
+      <c r="H206" s="19"/>
+      <c r="I206" s="19">
         <v>1616</v>
       </c>
-      <c r="L206" s="22" t="s">
+      <c r="M206" s="22" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="207" spans="1:14" ht="117.5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:15" ht="120" x14ac:dyDescent="0.2">
       <c r="A207" s="19" t="s">
         <v>789</v>
       </c>
       <c r="B207" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C207" s="19" t="s">
         <v>790</v>
       </c>
-      <c r="C207" s="19" t="s">
+      <c r="D207" s="19" t="s">
         <v>791</v>
       </c>
-      <c r="H207" s="19">
+      <c r="I207" s="19">
         <v>1627</v>
       </c>
-      <c r="L207" s="22" t="s">
+      <c r="M207" s="22" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A208" s="19" t="s">
         <v>793</v>
       </c>
-      <c r="B208" s="19"/>
-      <c r="C208" s="19" t="s">
+      <c r="B208" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C208" s="19"/>
+      <c r="D208" s="19" t="s">
         <v>794</v>
       </c>
-      <c r="N208" t="s">
+      <c r="O208" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="209" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A209" s="19" t="s">
         <v>796</v>
       </c>
-      <c r="B209" s="19"/>
-      <c r="C209" s="33" t="s">
+      <c r="B209" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C209" s="19"/>
+      <c r="D209" t="s">
         <v>797</v>
       </c>
-      <c r="N209" t="s">
+      <c r="O209" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="210" spans="1:15" ht="143.5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:16" ht="150" x14ac:dyDescent="0.2">
       <c r="A210" s="19" t="s">
         <v>798</v>
       </c>
       <c r="B210" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C210" s="19" t="s">
         <v>799</v>
       </c>
-      <c r="C210" s="19" t="s">
+      <c r="D210" s="19" t="s">
         <v>800</v>
       </c>
-      <c r="D210" s="33">
+      <c r="E210">
         <v>1569</v>
       </c>
-      <c r="E210" s="33"/>
-      <c r="F210" s="33"/>
-      <c r="G210" s="33"/>
-      <c r="H210" s="33">
+      <c r="I210">
         <v>1640</v>
       </c>
-      <c r="L210" s="22" t="s">
+      <c r="M210" s="22" t="s">
         <v>801</v>
       </c>
-      <c r="N210" s="19" t="s">
+      <c r="O210" s="19" t="s">
         <v>280</v>
       </c>
-      <c r="O210" s="41" t="s">
+      <c r="P210" s="29" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="211" spans="1:15" ht="65.5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:16" ht="60" x14ac:dyDescent="0.2">
       <c r="A211" s="19" t="s">
         <v>803</v>
       </c>
       <c r="B211" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C211" s="19" t="s">
         <v>804</v>
       </c>
-      <c r="C211" s="19" t="s">
+      <c r="D211" s="19" t="s">
         <v>805</v>
       </c>
-      <c r="D211" s="33">
+      <c r="E211">
         <v>1590</v>
       </c>
-      <c r="E211" s="33"/>
-      <c r="F211" s="33"/>
-      <c r="G211" s="33"/>
-      <c r="H211" s="33">
+      <c r="I211">
         <v>1621</v>
       </c>
-      <c r="L211" s="22" t="s">
+      <c r="M211" s="22" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A212" s="19" t="s">
         <v>807</v>
       </c>
-      <c r="B212" s="19"/>
-      <c r="C212" s="19" t="s">
+      <c r="B212" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C212" s="19"/>
+      <c r="D212" s="19" t="s">
         <v>808</v>
       </c>
-      <c r="D212" s="33">
+      <c r="E212">
         <v>1569</v>
       </c>
-      <c r="E212" s="33"/>
-      <c r="F212" s="33"/>
-      <c r="G212" s="33"/>
-      <c r="H212" s="33">
+      <c r="I212">
         <v>1642</v>
       </c>
     </row>
-    <row r="213" spans="1:15" ht="104.5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:16" ht="105" x14ac:dyDescent="0.2">
       <c r="A213" s="19" t="s">
         <v>809</v>
       </c>
       <c r="B213" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C213" s="19" t="s">
         <v>810</v>
       </c>
-      <c r="C213" s="19" t="s">
+      <c r="D213" s="19" t="s">
         <v>811</v>
       </c>
-      <c r="D213" s="33">
+      <c r="E213">
         <v>1574</v>
       </c>
-      <c r="E213" s="33"/>
-      <c r="F213" s="33"/>
-      <c r="G213" s="33"/>
-      <c r="H213" s="33">
+      <c r="I213">
         <v>1640</v>
       </c>
-      <c r="L213" s="22" t="s">
+      <c r="M213" s="22" t="s">
         <v>812</v>
       </c>
-      <c r="M213" s="22" t="s">
+      <c r="N213" s="22" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="214" spans="1:15" ht="91.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:16" ht="90" x14ac:dyDescent="0.2">
       <c r="A214" s="19" t="s">
         <v>814</v>
       </c>
       <c r="B214" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C214" s="19" t="s">
         <v>815</v>
       </c>
-      <c r="C214" s="19" t="s">
+      <c r="D214" s="19" t="s">
         <v>816</v>
       </c>
-      <c r="D214" s="33">
+      <c r="E214">
         <v>1595</v>
       </c>
-      <c r="E214" s="33"/>
-      <c r="F214" s="33"/>
-      <c r="G214" s="33"/>
-      <c r="H214" s="33">
+      <c r="I214">
         <v>1648</v>
       </c>
-      <c r="L214" s="22" t="s">
+      <c r="M214" s="22" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="215" spans="1:15" ht="87" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:16" ht="96" x14ac:dyDescent="0.2">
       <c r="A215" s="19" t="s">
         <v>818</v>
       </c>
-      <c r="B215" s="33"/>
-      <c r="C215" s="19" t="s">
+      <c r="B215" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D215" s="19" t="s">
         <v>819</v>
       </c>
-      <c r="D215" s="33">
+      <c r="E215">
         <v>1579</v>
       </c>
-      <c r="E215" s="33"/>
-      <c r="F215" s="33"/>
-      <c r="G215" s="33"/>
-      <c r="H215" s="33">
+      <c r="I215">
         <v>1626</v>
       </c>
-      <c r="I215" s="33"/>
-      <c r="J215" s="33"/>
-      <c r="K215" s="33"/>
-      <c r="L215" s="22" t="s">
+      <c r="M215" s="22" t="s">
         <v>820</v>
       </c>
-      <c r="O215" s="41" t="s">
+      <c r="P215" s="29" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="216" spans="1:15" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:16" ht="96" x14ac:dyDescent="0.2">
       <c r="A216" s="19" t="s">
         <v>822</v>
       </c>
-      <c r="B216" s="19"/>
-      <c r="C216" s="19" t="s">
+      <c r="B216" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C216" s="19"/>
+      <c r="D216" s="19" t="s">
         <v>823</v>
       </c>
-      <c r="L216" s="41" t="s">
+      <c r="M216" s="29" t="s">
         <v>824</v>
       </c>
-      <c r="O216" s="41" t="s">
+      <c r="P216" s="29" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="217" spans="1:15" ht="117.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:16" ht="120" x14ac:dyDescent="0.2">
       <c r="A217" s="19" t="s">
         <v>826</v>
       </c>
       <c r="B217" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C217" s="19" t="s">
         <v>827</v>
       </c>
-      <c r="C217" s="19" t="s">
+      <c r="D217" s="19" t="s">
         <v>828</v>
       </c>
-      <c r="D217" s="19">
+      <c r="E217" s="19">
         <v>1577</v>
       </c>
-      <c r="E217" s="19"/>
       <c r="F217" s="19"/>
       <c r="G217" s="19"/>
-      <c r="H217" s="19">
+      <c r="H217" s="19"/>
+      <c r="I217" s="19">
         <v>1645</v>
       </c>
-      <c r="L217" s="22" t="s">
+      <c r="M217" s="22" t="s">
         <v>829</v>
       </c>
-      <c r="M217" s="22" t="s">
+      <c r="N217" s="22" t="s">
         <v>830</v>
       </c>
-      <c r="N217" s="20" t="s">
+      <c r="O217" s="20" t="s">
         <v>831</v>
       </c>
-      <c r="O217" s="22" t="s">
+      <c r="P217" s="22" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A218" s="19" t="s">
         <v>833</v>
       </c>
-      <c r="B218" s="35" t="s">
+      <c r="B218" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C218" s="19" t="s">
         <v>834</v>
       </c>
-      <c r="C218" s="19" t="s">
+      <c r="D218" s="19" t="s">
         <v>835</v>
       </c>
-      <c r="N218" s="19" t="s">
+      <c r="O218" s="19" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A219" s="19" t="s">
         <v>836</v>
       </c>
       <c r="B219" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C219" s="19" t="s">
         <v>837</v>
       </c>
-      <c r="C219" s="19" t="s">
+      <c r="D219" s="19" t="s">
         <v>838</v>
       </c>
-      <c r="N219" s="19" t="s">
+      <c r="O219" s="19" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A220" s="19" t="s">
         <v>839</v>
       </c>
       <c r="B220" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C220" s="19" t="s">
         <v>840</v>
       </c>
-      <c r="C220" s="19" t="s">
+      <c r="D220" s="19" t="s">
         <v>841</v>
       </c>
-      <c r="N220" s="19" t="s">
+      <c r="O220" s="19" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A221" s="19" t="s">
         <v>842</v>
       </c>
       <c r="B221" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C221" s="19" t="s">
         <v>843</v>
       </c>
-      <c r="C221" s="19" t="s">
+      <c r="D221" s="19" t="s">
         <v>844</v>
       </c>
-      <c r="N221" s="19" t="s">
+      <c r="O221" s="19" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A222" s="19" t="s">
         <v>845</v>
       </c>
       <c r="B222" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C222" s="19" t="s">
         <v>846</v>
       </c>
-      <c r="C222" s="19" t="s">
+      <c r="D222" s="19" t="s">
         <v>847</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A223" s="33" t="s">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
         <v>848</v>
       </c>
       <c r="B223" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C223" t="s">
         <v>849</v>
       </c>
-      <c r="C223" t="s">
+      <c r="D223" t="s">
         <v>850</v>
       </c>
-      <c r="D223">
+      <c r="E223">
         <v>1582</v>
       </c>
-      <c r="H223">
+      <c r="I223">
         <v>1630</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A224" s="33" t="s">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
         <v>851</v>
       </c>
-      <c r="D224">
+      <c r="B224" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E224">
         <v>1591</v>
       </c>
-      <c r="H224">
+      <c r="I224">
         <v>1631</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>852</v>
       </c>
-      <c r="C225" t="s">
+      <c r="B225" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D225" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>854</v>
       </c>
-      <c r="C226" t="s">
+      <c r="B226" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D226" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>856</v>
       </c>
-      <c r="C227" t="s">
+      <c r="B227" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D227" t="s">
         <v>857</v>
       </c>
-      <c r="D227">
+      <c r="E227">
         <v>1590</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>858</v>
       </c>
-      <c r="C228" s="33" t="s">
+      <c r="B228" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D228" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="230" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B229" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="230" spans="1:16" ht="60" x14ac:dyDescent="0.2">
       <c r="A230" s="19" t="s">
         <v>860</v>
       </c>
       <c r="B230" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C230" s="19" t="s">
         <v>861</v>
       </c>
-      <c r="C230" s="19" t="s">
+      <c r="D230" s="19" t="s">
         <v>862</v>
       </c>
-      <c r="D230" s="19">
+      <c r="E230" s="19">
         <v>1556</v>
       </c>
-      <c r="E230" s="19"/>
       <c r="F230" s="19"/>
       <c r="G230" s="19"/>
-      <c r="H230" s="19">
+      <c r="H230" s="19"/>
+      <c r="I230" s="19">
         <v>1616</v>
       </c>
-      <c r="L230" s="22" t="s">
+      <c r="M230" s="22" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A231" s="19" t="s">
         <v>864</v>
       </c>
       <c r="B231" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C231" s="19" t="s">
         <v>865</v>
       </c>
-      <c r="C231" s="19" t="s">
+      <c r="D231" s="19" t="s">
         <v>866</v>
       </c>
-      <c r="D231" s="19">
+      <c r="E231" s="19">
         <v>1547</v>
       </c>
-      <c r="E231" s="19"/>
       <c r="F231" s="19"/>
       <c r="G231" s="19"/>
-      <c r="H231" s="19">
+      <c r="H231" s="19"/>
+      <c r="I231" s="19">
         <v>1623</v>
       </c>
     </row>
-    <row r="232" spans="1:15" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A232" s="19" t="s">
         <v>867</v>
       </c>
-      <c r="B232" s="19"/>
-      <c r="C232" s="19" t="s">
+      <c r="B232" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C232" s="19"/>
+      <c r="D232" s="19" t="s">
         <v>868</v>
       </c>
-      <c r="D232" s="19">
+      <c r="E232" s="19">
         <v>1550</v>
       </c>
-      <c r="E232" s="19"/>
       <c r="F232" s="19"/>
       <c r="G232" s="19"/>
-      <c r="H232" s="19">
+      <c r="H232" s="19"/>
+      <c r="I232" s="19">
         <v>1613</v>
       </c>
-      <c r="L232" s="22" t="s">
+      <c r="M232" s="22" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="233" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:16" ht="45" x14ac:dyDescent="0.2">
       <c r="A233" s="19" t="s">
         <v>870</v>
       </c>
-      <c r="B233" s="19"/>
-      <c r="C233" s="19" t="s">
+      <c r="B233" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C233" s="19"/>
+      <c r="D233" s="19" t="s">
         <v>871</v>
       </c>
-      <c r="D233" s="19"/>
       <c r="E233" s="19"/>
       <c r="F233" s="19"/>
       <c r="G233" s="19"/>
-      <c r="H233" s="19">
+      <c r="H233" s="19"/>
+      <c r="I233" s="19">
         <v>1607</v>
       </c>
-      <c r="I233" s="19"/>
       <c r="J233" s="19"/>
       <c r="K233" s="19"/>
-      <c r="L233" s="22" t="s">
+      <c r="L233" s="19"/>
+      <c r="M233" s="22" t="s">
         <v>872</v>
       </c>
     </row>
-    <row r="234" spans="1:15" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:16" ht="96" x14ac:dyDescent="0.2">
       <c r="A234" s="19" t="s">
         <v>873</v>
       </c>
       <c r="B234" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C234" s="19" t="s">
         <v>874</v>
       </c>
-      <c r="C234" s="19" t="s">
+      <c r="D234" s="19" t="s">
         <v>875</v>
       </c>
-      <c r="O234" s="30" t="s">
+      <c r="P234" s="29" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="235" spans="1:15" ht="78.5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:16" ht="75" x14ac:dyDescent="0.2">
       <c r="A235" s="19" t="s">
         <v>877</v>
       </c>
-      <c r="B235" s="19"/>
-      <c r="C235" s="19" t="s">
+      <c r="B235" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C235" s="19"/>
+      <c r="D235" s="19" t="s">
         <v>878</v>
       </c>
-      <c r="D235" s="19">
+      <c r="E235" s="19">
         <v>1590</v>
       </c>
-      <c r="E235" s="19"/>
       <c r="F235" s="19"/>
       <c r="G235" s="19"/>
-      <c r="H235" s="19">
+      <c r="H235" s="19"/>
+      <c r="I235" s="19">
         <v>1618</v>
       </c>
-      <c r="I235" s="19"/>
       <c r="J235" s="19"/>
       <c r="K235" s="19"/>
-      <c r="L235" s="22" t="s">
+      <c r="L235" s="19"/>
+      <c r="M235" s="22" t="s">
         <v>879</v>
       </c>
     </row>
-    <row r="236" spans="1:15" ht="78.5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:16" ht="75" x14ac:dyDescent="0.2">
       <c r="A236" s="19" t="s">
         <v>880</v>
       </c>
       <c r="B236" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C236" s="19" t="s">
         <v>881</v>
       </c>
-      <c r="C236" s="19" t="s">
+      <c r="D236" s="19" t="s">
         <v>882</v>
       </c>
-      <c r="D236" s="19">
+      <c r="E236" s="19">
         <v>1587</v>
       </c>
-      <c r="E236" s="19"/>
       <c r="F236" s="19"/>
       <c r="G236" s="19"/>
-      <c r="H236" s="19">
+      <c r="H236" s="19"/>
+      <c r="I236" s="19">
         <v>1640</v>
       </c>
-      <c r="I236" s="19"/>
-      <c r="L236" s="22" t="s">
+      <c r="J236" s="19"/>
+      <c r="M236" s="22" t="s">
         <v>883</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A237" s="19" t="s">
         <v>884</v>
       </c>
-      <c r="C237" s="19" t="s">
+      <c r="B237" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D237" s="19" t="s">
         <v>885</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A238" s="19" t="s">
         <v>886</v>
       </c>
-      <c r="C238" s="19" t="s">
+      <c r="B238" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D238" s="19" t="s">
         <v>887</v>
       </c>
     </row>
-    <row r="239" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:16" ht="80" x14ac:dyDescent="0.2">
       <c r="A239" s="19" t="s">
         <v>888</v>
       </c>
-      <c r="C239" s="19" t="s">
+      <c r="B239" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D239" s="19" t="s">
         <v>889</v>
       </c>
-      <c r="D239" s="19">
+      <c r="E239" s="19">
         <v>1564</v>
       </c>
-      <c r="E239" s="19"/>
       <c r="F239" s="19"/>
       <c r="G239" s="19"/>
-      <c r="H239" s="19">
+      <c r="H239" s="19"/>
+      <c r="I239" s="19">
         <v>1629</v>
       </c>
-      <c r="O239" s="41" t="s">
+      <c r="P239" s="29" t="s">
         <v>890</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A240" s="19" t="s">
         <v>891</v>
       </c>
-      <c r="C240" s="19" t="s">
+      <c r="B240" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D240" s="19" t="s">
         <v>892</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A241" s="19" t="s">
         <v>893</v>
       </c>
-      <c r="C241" s="19" t="s">
+      <c r="B241" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D241" s="19" t="s">
         <v>892</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A242" s="19" t="s">
         <v>894</v>
       </c>
-      <c r="C242" s="19" t="s">
+      <c r="B242" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D242" s="19" t="s">
         <v>895</v>
       </c>
-      <c r="D242" s="19">
+      <c r="E242" s="19">
         <v>1600</v>
       </c>
-      <c r="E242" s="19"/>
       <c r="F242" s="19"/>
       <c r="G242" s="19"/>
-      <c r="H242" s="19">
+      <c r="H242" s="19"/>
+      <c r="I242" s="19">
         <v>1649</v>
       </c>
     </row>
-    <row r="243" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A243" s="19" t="s">
         <v>896</v>
       </c>
-      <c r="B243" s="19"/>
-      <c r="C243" s="19" t="s">
+      <c r="B243" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C243" s="19"/>
+      <c r="D243" s="19" t="s">
         <v>897</v>
       </c>
-      <c r="D243" s="19">
+      <c r="E243" s="19">
         <v>1606</v>
       </c>
-      <c r="E243" s="19"/>
       <c r="F243" s="19"/>
       <c r="G243" s="19"/>
-      <c r="H243" s="19">
+      <c r="H243" s="19"/>
+      <c r="I243" s="19">
         <v>1646</v>
       </c>
-      <c r="L243" s="22" t="s">
+      <c r="M243" s="22" t="s">
         <v>898</v>
       </c>
     </row>
-    <row r="244" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:16" ht="60" x14ac:dyDescent="0.2">
       <c r="A244" s="19" t="s">
         <v>899</v>
       </c>
       <c r="B244" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C244" s="19" t="s">
         <v>900</v>
       </c>
-      <c r="C244" s="19" t="s">
+      <c r="D244" s="19" t="s">
         <v>720</v>
       </c>
-      <c r="D244" s="19"/>
       <c r="E244" s="19"/>
       <c r="F244" s="19"/>
       <c r="G244" s="19"/>
       <c r="H244" s="19"/>
-      <c r="L244" s="22" t="s">
+      <c r="I244" s="19"/>
+      <c r="M244" s="22" t="s">
         <v>901</v>
       </c>
-      <c r="M244" s="22"/>
-      <c r="O244" s="22" t="s">
+      <c r="N244" s="22"/>
+      <c r="P244" s="22" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="245" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:16" ht="60" x14ac:dyDescent="0.2">
       <c r="A245" s="19" t="s">
         <v>903</v>
       </c>
       <c r="B245" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C245" s="19" t="s">
         <v>900</v>
       </c>
-      <c r="C245" s="19" t="s">
+      <c r="D245" s="19" t="s">
         <v>720</v>
       </c>
-      <c r="D245" s="19"/>
       <c r="E245" s="19"/>
       <c r="F245" s="19"/>
       <c r="G245" s="19"/>
       <c r="H245" s="19"/>
-      <c r="L245" s="22" t="s">
+      <c r="I245" s="19"/>
+      <c r="M245" s="22" t="s">
         <v>904</v>
       </c>
-      <c r="M245" s="22"/>
-      <c r="O245" s="22" t="s">
+      <c r="N245" s="22"/>
+      <c r="P245" s="22" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="246" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:16" ht="60" x14ac:dyDescent="0.2">
       <c r="A246" s="19" t="s">
         <v>905</v>
       </c>
-      <c r="B246" s="19"/>
-      <c r="C246" s="19" t="s">
+      <c r="B246" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C246" s="19"/>
+      <c r="D246" s="19" t="s">
         <v>906</v>
       </c>
-      <c r="D246" s="19"/>
       <c r="E246" s="19"/>
       <c r="F246" s="19"/>
       <c r="G246" s="19"/>
       <c r="H246" s="19"/>
-      <c r="L246" s="22" t="s">
+      <c r="I246" s="19"/>
+      <c r="M246" s="22" t="s">
         <v>907</v>
       </c>
-      <c r="M246" s="22" t="s">
+      <c r="N246" s="22" t="s">
         <v>908</v>
       </c>
-      <c r="O246" s="22" t="s">
+      <c r="P246" s="22" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="247" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:16" ht="80" x14ac:dyDescent="0.2">
       <c r="A247" s="19" t="s">
         <v>909</v>
       </c>
-      <c r="B247" s="19"/>
-      <c r="C247" s="19" t="s">
+      <c r="B247" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C247" s="19"/>
+      <c r="D247" s="19" t="s">
         <v>910</v>
       </c>
-      <c r="D247" s="19">
+      <c r="E247" s="19">
         <v>1572</v>
       </c>
-      <c r="E247" s="19"/>
       <c r="F247" s="19"/>
       <c r="G247" s="19"/>
-      <c r="H247" s="19">
+      <c r="H247" s="19"/>
+      <c r="I247" s="19">
         <v>1647</v>
       </c>
-      <c r="O247" s="41" t="s">
+      <c r="P247" s="29" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A248" s="19" t="s">
         <v>912</v>
       </c>
       <c r="B248" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C248" s="19" t="s">
         <v>913</v>
       </c>
-      <c r="C248" s="19" t="s">
+      <c r="D248" s="19" t="s">
         <v>914</v>
       </c>
     </row>
-    <row r="249" spans="1:15" ht="174" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:16" ht="160" x14ac:dyDescent="0.2">
       <c r="A249" s="19" t="s">
         <v>915</v>
       </c>
       <c r="B249" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C249" s="19" t="s">
         <v>916</v>
       </c>
-      <c r="C249" s="19" t="s">
+      <c r="D249" s="19" t="s">
         <v>917</v>
       </c>
-      <c r="D249" s="19"/>
       <c r="E249" s="19"/>
       <c r="F249" s="19"/>
       <c r="G249" s="19"/>
       <c r="H249" s="19"/>
-      <c r="O249" s="41" t="s">
+      <c r="I249" s="19"/>
+      <c r="P249" s="29" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="250" spans="1:15" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A250" s="19" t="s">
         <v>919</v>
       </c>
-      <c r="B250" s="19"/>
-      <c r="C250" s="19" t="s">
+      <c r="B250" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C250" s="19"/>
+      <c r="D250" s="19" t="s">
         <v>374</v>
       </c>
-      <c r="L250" s="22" t="s">
+      <c r="M250" s="22" t="s">
         <v>920</v>
       </c>
-      <c r="N250" s="19" t="s">
+      <c r="O250" s="19" t="s">
         <v>921</v>
       </c>
     </row>
-    <row r="251" spans="1:15" ht="78.5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:16" ht="75" x14ac:dyDescent="0.2">
       <c r="A251" s="19" t="s">
         <v>922</v>
       </c>
       <c r="B251" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C251" s="19" t="s">
         <v>923</v>
       </c>
-      <c r="C251" s="19" t="s">
+      <c r="D251" s="19" t="s">
         <v>924</v>
       </c>
-      <c r="D251" s="19">
+      <c r="E251" s="19">
         <v>1582</v>
       </c>
-      <c r="E251" s="19"/>
       <c r="F251" s="19"/>
       <c r="G251" s="19"/>
-      <c r="H251" s="19">
+      <c r="H251" s="19"/>
+      <c r="I251" s="19">
         <v>1616</v>
       </c>
-      <c r="L251" s="22" t="s">
+      <c r="M251" s="22" t="s">
         <v>925</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A252" s="19" t="s">
         <v>926</v>
       </c>
-      <c r="B252" s="19"/>
-      <c r="C252" s="19" t="s">
+      <c r="B252" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C252" s="19"/>
+      <c r="D252" s="19" t="s">
         <v>927</v>
       </c>
-      <c r="D252" s="19">
+      <c r="E252" s="19">
         <v>1540</v>
       </c>
-      <c r="E252" s="19"/>
       <c r="F252" s="19"/>
       <c r="G252" s="19"/>
-      <c r="H252" s="19">
+      <c r="H252" s="19"/>
+      <c r="I252" s="19">
         <v>1596</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A253" s="19" t="s">
         <v>928</v>
       </c>
-      <c r="B253" s="19"/>
-      <c r="C253" s="19" t="s">
+      <c r="B253" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C253" s="19"/>
+      <c r="D253" s="19" t="s">
         <v>929</v>
       </c>
-      <c r="D253" s="19"/>
       <c r="E253" s="19"/>
       <c r="F253" s="19"/>
       <c r="G253" s="19"/>
@@ -9281,20 +10021,23 @@
       <c r="I253" s="19"/>
       <c r="J253" s="19"/>
       <c r="K253" s="19"/>
-      <c r="L253" s="22"/>
+      <c r="L253" s="19"/>
       <c r="M253" s="22"/>
-    </row>
-    <row r="254" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+      <c r="N253" s="22"/>
+    </row>
+    <row r="254" spans="1:16" ht="60" x14ac:dyDescent="0.2">
       <c r="A254" s="19" t="s">
         <v>930</v>
       </c>
       <c r="B254" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C254" s="19" t="s">
         <v>931</v>
       </c>
-      <c r="C254" s="19" t="s">
+      <c r="D254" s="19" t="s">
         <v>932</v>
       </c>
-      <c r="D254" s="19"/>
       <c r="E254" s="19"/>
       <c r="F254" s="19"/>
       <c r="G254" s="19"/>
@@ -9302,288 +10045,333 @@
       <c r="I254" s="19"/>
       <c r="J254" s="19"/>
       <c r="K254" s="19"/>
-      <c r="L254" s="22"/>
-      <c r="M254" s="22" t="s">
+      <c r="L254" s="19"/>
+      <c r="M254" s="22"/>
+      <c r="N254" s="22" t="s">
         <v>933</v>
       </c>
-      <c r="N254" s="19" t="s">
+      <c r="O254" s="19" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="255" spans="1:15" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:16" ht="144" x14ac:dyDescent="0.2">
       <c r="A255" s="19" t="s">
         <v>934</v>
       </c>
       <c r="B255" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C255" s="19" t="s">
         <v>935</v>
       </c>
-      <c r="C255" s="19" t="s">
+      <c r="D255" s="19" t="s">
         <v>936</v>
       </c>
-      <c r="D255" s="19">
+      <c r="E255" s="19">
         <v>1571</v>
       </c>
-      <c r="E255" s="19"/>
       <c r="F255" s="19"/>
       <c r="G255" s="19"/>
-      <c r="H255" s="19">
+      <c r="H255" s="19"/>
+      <c r="I255" s="19">
         <v>1628</v>
       </c>
-      <c r="O255" s="41" t="s">
+      <c r="P255" s="29" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A256" s="19" t="s">
         <v>938</v>
       </c>
       <c r="B256" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C256" s="19" t="s">
         <v>939</v>
       </c>
-      <c r="C256" s="19" t="s">
+      <c r="D256" s="19" t="s">
         <v>940</v>
       </c>
-      <c r="D256" s="19">
+      <c r="E256" s="19">
         <v>1558</v>
       </c>
-      <c r="E256" s="19"/>
       <c r="F256" s="19"/>
       <c r="G256" s="19"/>
-      <c r="H256" s="19">
+      <c r="H256" s="19"/>
+      <c r="I256" s="19">
         <v>1614</v>
       </c>
     </row>
-    <row r="257" spans="1:15" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A257" s="19" t="s">
         <v>941</v>
       </c>
       <c r="B257" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C257" s="19" t="s">
         <v>942</v>
       </c>
-      <c r="C257" s="19"/>
-      <c r="D257" s="19">
+      <c r="D257" s="19"/>
+      <c r="E257" s="19">
         <v>1588</v>
       </c>
-      <c r="E257" s="19"/>
       <c r="F257" s="19"/>
       <c r="G257" s="19"/>
-      <c r="H257" s="19">
+      <c r="H257" s="19"/>
+      <c r="I257" s="19">
         <v>1631</v>
       </c>
-      <c r="I257" s="19"/>
       <c r="J257" s="19"/>
       <c r="K257" s="19"/>
-      <c r="L257" s="22"/>
-      <c r="M257" s="22" t="s">
+      <c r="L257" s="19"/>
+      <c r="M257" s="22"/>
+      <c r="N257" s="22" t="s">
         <v>943</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A258" s="19" t="s">
         <v>944</v>
       </c>
       <c r="B258" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C258" s="19" t="s">
         <v>945</v>
       </c>
-      <c r="C258" s="19" t="s">
+      <c r="D258" s="19" t="s">
         <v>946</v>
       </c>
-      <c r="D258" s="19">
+      <c r="E258" s="19">
         <v>1554</v>
       </c>
-      <c r="E258" s="19"/>
       <c r="F258" s="19"/>
       <c r="G258" s="19"/>
-      <c r="H258" s="19">
+      <c r="H258" s="19"/>
+      <c r="I258" s="19">
         <v>1611</v>
       </c>
-      <c r="I258" s="19"/>
-    </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="J258" s="19"/>
+    </row>
+    <row r="259" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A259" s="19" t="s">
         <v>947</v>
       </c>
       <c r="B259" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C259" s="19" t="s">
         <v>948</v>
       </c>
-      <c r="C259" s="19" t="s">
+      <c r="D259" s="19" t="s">
         <v>946</v>
       </c>
-      <c r="D259" s="19">
+      <c r="E259" s="19">
         <v>1578</v>
       </c>
-      <c r="E259" s="19"/>
       <c r="F259" s="19"/>
       <c r="G259" s="19"/>
-      <c r="H259" s="19">
+      <c r="H259" s="19"/>
+      <c r="I259" s="19">
         <v>1621</v>
       </c>
-      <c r="I259" s="19"/>
-    </row>
-    <row r="260" spans="1:15" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="J259" s="19"/>
+    </row>
+    <row r="260" spans="1:16" ht="30" x14ac:dyDescent="0.2">
       <c r="A260" s="19" t="s">
         <v>949</v>
       </c>
       <c r="B260" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C260" s="19" t="s">
         <v>950</v>
       </c>
-      <c r="C260" s="19" t="s">
+      <c r="D260" s="19" t="s">
         <v>951</v>
       </c>
-      <c r="F260" s="19"/>
-      <c r="G260" s="19" t="s">
+      <c r="G260" s="19"/>
+      <c r="H260" s="19" t="s">
         <v>952</v>
       </c>
-      <c r="H260" s="19">
+      <c r="I260" s="19">
         <v>1625</v>
       </c>
-      <c r="I260" s="19"/>
-      <c r="N260" s="20" t="s">
+      <c r="J260" s="19"/>
+      <c r="O260" s="20" t="s">
         <v>953</v>
       </c>
     </row>
-    <row r="261" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:16" ht="64" x14ac:dyDescent="0.2">
       <c r="A261" s="19" t="s">
         <v>954</v>
       </c>
       <c r="B261" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C261" s="19" t="s">
         <v>955</v>
       </c>
-      <c r="C261" s="19" t="s">
+      <c r="D261" s="19" t="s">
         <v>956</v>
       </c>
-      <c r="D261" s="19">
+      <c r="E261" s="19">
         <v>1556</v>
       </c>
-      <c r="E261" s="19"/>
       <c r="F261" s="19"/>
       <c r="G261" s="19"/>
-      <c r="H261" s="19">
+      <c r="H261" s="19"/>
+      <c r="I261" s="19">
         <v>1624</v>
       </c>
-      <c r="O261" s="41" t="s">
+      <c r="P261" s="29" t="s">
         <v>957</v>
       </c>
     </row>
-    <row r="262" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:16" ht="60" x14ac:dyDescent="0.2">
       <c r="A262" s="19" t="s">
         <v>958</v>
       </c>
-      <c r="B262" s="19"/>
-      <c r="C262" s="19" t="s">
+      <c r="B262" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C262" s="19"/>
+      <c r="D262" s="19" t="s">
         <v>959</v>
       </c>
-      <c r="M262" s="22" t="s">
+      <c r="N262" s="22" t="s">
         <v>960</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A263" s="19" t="s">
         <v>961</v>
       </c>
       <c r="B263" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C263" s="19" t="s">
         <v>962</v>
       </c>
-      <c r="C263" s="19" t="s">
+      <c r="D263" s="19" t="s">
         <v>963</v>
       </c>
     </row>
-    <row r="264" spans="1:15" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:16" ht="60" x14ac:dyDescent="0.2">
       <c r="A264" s="19" t="s">
         <v>964</v>
       </c>
-      <c r="C264" s="19" t="s">
+      <c r="B264" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D264" s="19" t="s">
         <v>360</v>
       </c>
-      <c r="L264" s="22" t="s">
+      <c r="M264" s="22" t="s">
         <v>965</v>
       </c>
     </row>
-    <row r="265" spans="1:15" ht="203" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:16" ht="208" x14ac:dyDescent="0.2">
       <c r="A265" s="19" t="s">
         <v>966</v>
       </c>
       <c r="B265" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C265" s="19" t="s">
         <v>967</v>
       </c>
-      <c r="C265" s="19" t="s">
+      <c r="D265" s="19" t="s">
         <v>968</v>
       </c>
-      <c r="D265" s="19">
+      <c r="E265" s="19">
         <v>1568</v>
       </c>
-      <c r="E265" s="19"/>
       <c r="F265" s="19"/>
       <c r="G265" s="19"/>
-      <c r="H265" s="19">
+      <c r="H265" s="19"/>
+      <c r="I265" s="19">
         <v>1624</v>
       </c>
-      <c r="M265" s="22" t="s">
+      <c r="N265" s="22" t="s">
         <v>969</v>
       </c>
-      <c r="N265" s="19" t="s">
+      <c r="O265" s="19" t="s">
         <v>970</v>
       </c>
-      <c r="O265" s="41" t="s">
+      <c r="P265" s="29" t="s">
         <v>971</v>
       </c>
     </row>
-    <row r="266" spans="1:15" ht="78.5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:16" ht="75" x14ac:dyDescent="0.2">
       <c r="A266" s="19" t="s">
         <v>972</v>
       </c>
       <c r="B266" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C266" s="19" t="s">
         <v>973</v>
       </c>
-      <c r="C266" s="19" t="s">
+      <c r="D266" s="19" t="s">
         <v>974</v>
       </c>
-      <c r="D266" s="19">
+      <c r="E266" s="19">
         <v>1554</v>
       </c>
-      <c r="E266" s="19"/>
       <c r="F266" s="19"/>
       <c r="G266" s="19"/>
-      <c r="H266" s="19">
+      <c r="H266" s="19"/>
+      <c r="I266" s="19">
         <v>1642</v>
       </c>
-      <c r="L266" s="22" t="s">
+      <c r="M266" s="22" t="s">
         <v>975</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A267" s="19" t="s">
         <v>976</v>
       </c>
       <c r="B267" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C267" s="19" t="s">
         <v>977</v>
       </c>
-      <c r="C267" s="19" t="s">
+      <c r="D267" s="19" t="s">
         <v>978</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A268" s="19" t="s">
         <v>979</v>
       </c>
       <c r="B268" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C268" s="19" t="s">
         <v>980</v>
       </c>
-      <c r="C268" s="19" t="s">
+      <c r="D268" s="19" t="s">
         <v>981</v>
       </c>
     </row>
-    <row r="269" spans="1:15" ht="91.5" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:16" ht="90" x14ac:dyDescent="0.2">
       <c r="A269" s="19" t="s">
         <v>982</v>
       </c>
       <c r="B269" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C269" s="19" t="s">
         <v>983</v>
       </c>
-      <c r="C269" s="19" t="s">
+      <c r="D269" s="19" t="s">
         <v>984</v>
       </c>
-      <c r="D269" s="19"/>
       <c r="E269" s="19"/>
       <c r="F269" s="19"/>
       <c r="G269" s="19"/>
@@ -9591,249 +10379,300 @@
       <c r="I269" s="19"/>
       <c r="J269" s="19"/>
       <c r="K269" s="19"/>
-      <c r="L269" s="22" t="s">
+      <c r="L269" s="19"/>
+      <c r="M269" s="22" t="s">
         <v>985</v>
       </c>
-      <c r="M269" s="22" t="s">
+      <c r="N269" s="22" t="s">
         <v>986</v>
       </c>
-      <c r="N269" t="s">
+      <c r="O269" t="s">
         <v>987</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A270" s="19" t="s">
         <v>988</v>
       </c>
-      <c r="B270" s="19"/>
-      <c r="C270" s="19" t="s">
+      <c r="B270" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C270" s="19"/>
+      <c r="D270" s="19" t="s">
         <v>989</v>
       </c>
-      <c r="D270" s="19">
+      <c r="E270" s="19">
         <v>1567</v>
       </c>
-      <c r="E270" s="19"/>
       <c r="F270" s="19"/>
       <c r="G270" s="19"/>
-      <c r="H270" s="19">
+      <c r="H270" s="19"/>
+      <c r="I270" s="19">
         <v>1626</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A271" s="19" t="s">
         <v>990</v>
       </c>
-      <c r="C271" s="19" t="s">
+      <c r="B271" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D271" s="19" t="s">
         <v>991</v>
       </c>
-      <c r="D271" s="19">
+      <c r="E271" s="19">
         <v>1587</v>
       </c>
-      <c r="E271" s="19"/>
       <c r="F271" s="19"/>
       <c r="G271" s="19"/>
-      <c r="H271" s="19">
+      <c r="H271" s="19"/>
+      <c r="I271" s="19">
         <v>1619</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A272" s="19" t="s">
         <v>992</v>
       </c>
       <c r="B272" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C272" s="19" t="s">
         <v>993</v>
       </c>
-      <c r="C272" s="19" t="s">
+      <c r="D272" s="19" t="s">
         <v>994</v>
       </c>
-      <c r="D272" s="19">
+      <c r="E272" s="19">
         <v>1525</v>
       </c>
-      <c r="E272" s="19"/>
       <c r="F272" s="19"/>
       <c r="G272" s="19"/>
-      <c r="H272" s="19">
+      <c r="H272" s="19"/>
+      <c r="I272" s="19">
         <v>1610</v>
       </c>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A273" s="36" t="s">
+    <row r="273" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A273" s="32" t="s">
         <v>995</v>
       </c>
-      <c r="B273" s="36" t="s">
+      <c r="B273" s="32" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C273" s="32" t="s">
         <v>996</v>
       </c>
-      <c r="C273" s="36" t="s">
+      <c r="D273" s="32" t="s">
         <v>997</v>
       </c>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A274" s="36" t="s">
+    <row r="274" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A274" s="32" t="s">
         <v>998</v>
       </c>
-      <c r="B274" s="36" t="s">
+      <c r="B274" s="32" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C274" s="32" t="s">
         <v>999</v>
       </c>
-      <c r="C274" s="36" t="s">
+      <c r="D274" s="32" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>1001</v>
       </c>
-      <c r="C275" s="36" t="s">
+      <c r="B275" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D275" s="32" t="s">
         <v>1002</v>
       </c>
     </row>
-    <row r="276" spans="1:14" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A276" s="33" t="s">
+    <row r="276" spans="1:15" ht="112" x14ac:dyDescent="0.2">
+      <c r="A276" t="s">
         <v>1003</v>
       </c>
-      <c r="B276" s="33"/>
-      <c r="L276" s="30" t="s">
+      <c r="B276" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M276" s="29" t="s">
         <v>1004</v>
       </c>
     </row>
-    <row r="277" spans="1:14" ht="116" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:15" ht="112" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>1005</v>
       </c>
-      <c r="C277" s="25" t="s">
+      <c r="B277" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D277" s="25" t="s">
         <v>1006</v>
       </c>
-      <c r="M277" s="30" t="s">
+      <c r="N277" s="29" t="s">
         <v>1007</v>
       </c>
-      <c r="N277" s="25" t="s">
+      <c r="O277" s="25" t="s">
         <v>1008</v>
       </c>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>1009</v>
       </c>
-      <c r="C278" t="s">
+      <c r="B278" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D278" t="s">
         <v>1010</v>
       </c>
     </row>
-    <row r="279" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:15" ht="64" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>1011</v>
       </c>
-      <c r="B279" s="21" t="s">
+      <c r="B279" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C279" s="21" t="s">
         <v>1012</v>
       </c>
-      <c r="C279" s="30" t="s">
+      <c r="D279" s="29" t="s">
         <v>1013</v>
       </c>
     </row>
-    <row r="280" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="B280" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C280" t="s">
         <v>1014</v>
       </c>
-      <c r="C280" s="30" t="s">
+      <c r="D280" s="29" t="s">
         <v>1015</v>
       </c>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>1016</v>
       </c>
-      <c r="C281" s="36" t="s">
+      <c r="B281" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D281" s="32" t="s">
         <v>1017</v>
       </c>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>1018</v>
       </c>
-      <c r="C282" t="s">
+      <c r="B282" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D282" t="s">
         <v>1019</v>
       </c>
     </row>
-    <row r="283" spans="1:14" ht="48.5" x14ac:dyDescent="0.35">
-      <c r="A283" s="36" t="s">
+    <row r="283" spans="1:15" ht="40" x14ac:dyDescent="0.2">
+      <c r="A283" s="32" t="s">
         <v>1032</v>
       </c>
-      <c r="B283" s="36" t="s">
+      <c r="B283" s="32" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C283" s="32" t="s">
         <v>1020</v>
       </c>
-      <c r="C283" s="37" t="s">
+      <c r="D283" s="33" t="s">
         <v>1021</v>
       </c>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>1022</v>
       </c>
       <c r="B284" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C284" t="s">
         <v>1023</v>
       </c>
-      <c r="C284" s="38" t="s">
+      <c r="D284" s="34" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A285" s="33" t="s">
+    <row r="285" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A285" t="s">
         <v>1024</v>
       </c>
-      <c r="B285" s="33" t="s">
+      <c r="B285" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C285" t="s">
         <v>1025</v>
       </c>
-      <c r="C285" t="s">
+      <c r="D285" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>1027</v>
       </c>
       <c r="B286" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C286" t="s">
         <v>1028</v>
       </c>
-      <c r="C286" t="s">
+      <c r="D286" t="s">
         <v>1029</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="O24" r:id="rId1" location="ndbcontent"/>
-    <hyperlink ref="O25" r:id="rId2"/>
-    <hyperlink ref="O45" r:id="rId3"/>
-    <hyperlink ref="O47" r:id="rId4"/>
-    <hyperlink ref="O48" r:id="rId5" location="v=onepage&amp;q=camillo%20taffin&amp;f=false"/>
-    <hyperlink ref="O50" r:id="rId6"/>
-    <hyperlink ref="M73" r:id="rId7"/>
-    <hyperlink ref="O93" r:id="rId8"/>
-    <hyperlink ref="O94" r:id="rId9"/>
-    <hyperlink ref="O96" r:id="rId10"/>
-    <hyperlink ref="O99" r:id="rId11"/>
-    <hyperlink ref="O124" r:id="rId12"/>
-    <hyperlink ref="O126" r:id="rId13" location="no117"/>
-    <hyperlink ref="O134" r:id="rId14"/>
-    <hyperlink ref="O141" r:id="rId15" location="v=onepage&amp;q=pack&amp;f=false"/>
-    <hyperlink ref="O142" r:id="rId16" location="v=onepage&amp;q=pack&amp;f=false"/>
-    <hyperlink ref="O143" r:id="rId17"/>
-    <hyperlink ref="O144" r:id="rId18"/>
-    <hyperlink ref="O145" r:id="rId19" location="adbcontent"/>
-    <hyperlink ref="O147" r:id="rId20" location="adbcontent"/>
-    <hyperlink ref="O148" r:id="rId21"/>
-    <hyperlink ref="O159" r:id="rId22"/>
-    <hyperlink ref="O173" r:id="rId23"/>
-    <hyperlink ref="O179" r:id="rId24"/>
-    <hyperlink ref="O183" r:id="rId25" location="v=onepage&amp;q=melchior%20noirot&amp;f=false"/>
-    <hyperlink ref="O185" r:id="rId26" location="v=onepage&amp;q=castre&amp;f=false"/>
-    <hyperlink ref="O186" r:id="rId27" location="v=onepage&amp;q=castre&amp;f=false"/>
-    <hyperlink ref="O187" r:id="rId28" location="v=onepage&amp;q=castre&amp;f=false"/>
-    <hyperlink ref="O210" r:id="rId29"/>
-    <hyperlink ref="O215" r:id="rId30"/>
-    <hyperlink ref="O217" r:id="rId31"/>
-    <hyperlink ref="O234" r:id="rId32"/>
-    <hyperlink ref="O239" r:id="rId33"/>
-    <hyperlink ref="O247" r:id="rId34"/>
-    <hyperlink ref="O255" r:id="rId35"/>
-    <hyperlink ref="O261" r:id="rId36"/>
+    <hyperlink ref="P24" r:id="rId1" location="ndbcontent" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="P25" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="P45" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="P47" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="P48" r:id="rId5" location="v=onepage&amp;q=camillo%20taffin&amp;f=false" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="P50" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N73" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="P93" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="P94" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="P96" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="P99" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="P124" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="P126" r:id="rId13" location="no117" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="P134" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="P141" r:id="rId15" location="v=onepage&amp;q=pack&amp;f=false" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="P142" r:id="rId16" location="v=onepage&amp;q=pack&amp;f=false" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="P143" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="P144" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="P145" r:id="rId19" location="adbcontent" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="P147" r:id="rId20" location="adbcontent" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="P148" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="P159" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="P173" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="P179" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="P183" r:id="rId25" location="v=onepage&amp;q=melchior%20noirot&amp;f=false" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="P185" r:id="rId26" location="v=onepage&amp;q=castre&amp;f=false" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="P186" r:id="rId27" location="v=onepage&amp;q=castre&amp;f=false" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="P187" r:id="rId28" location="v=onepage&amp;q=castre&amp;f=false" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="P210" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="P215" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="P217" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="P234" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="P239" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="P247" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="P255" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="P261" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId37"/>
